--- a/data/T3_follower_cleaned.xlsx
+++ b/data/T3_follower_cleaned.xlsx
@@ -1863,7 +1863,7 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S2">
         <v>3</v>
@@ -1872,10 +1872,10 @@
         <v>3</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W2">
         <v>6</v>
@@ -1913,7 +1913,7 @@
         <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <v>6</v>
@@ -1946,16 +1946,16 @@
         <v>5</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R3">
         <v>4</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U3">
         <v>5</v>
@@ -2035,10 +2035,10 @@
         <v>4</v>
       </c>
       <c r="R4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T4">
         <v>4</v>
@@ -2056,7 +2056,7 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z4">
         <v>4</v>
@@ -2088,7 +2088,7 @@
         <v>3</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -2186,13 +2186,13 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>5</v>
       </c>
       <c r="M6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -2225,13 +2225,13 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA6">
         <v>3</v>
@@ -2293,7 +2293,7 @@
         <v>5</v>
       </c>
       <c r="R7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>6</v>
@@ -2305,7 +2305,7 @@
         <v>4</v>
       </c>
       <c r="V7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -2355,7 +2355,7 @@
         <v>3</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -2376,10 +2376,10 @@
         <v>5</v>
       </c>
       <c r="Q8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8">
         <v>4</v>
@@ -2388,16 +2388,16 @@
         <v>4</v>
       </c>
       <c r="U8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W8">
         <v>6</v>
       </c>
       <c r="X8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y8">
         <v>3</v>
@@ -2426,7 +2426,7 @@
         <v>117</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>4</v>
@@ -2462,7 +2462,7 @@
         <v>4</v>
       </c>
       <c r="Q9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R9">
         <v>5</v>
@@ -2521,7 +2521,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>4</v>
@@ -2551,37 +2551,37 @@
         <v>6</v>
       </c>
       <c r="R10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>6</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U10">
         <v>5</v>
       </c>
       <c r="V10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>6</v>
       </c>
       <c r="X10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y10">
         <v>3</v>
       </c>
       <c r="Z10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA10">
         <v>4</v>
       </c>
       <c r="AB10">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:28">
@@ -2610,10 +2610,10 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11">
         <v>4</v>
@@ -2628,16 +2628,16 @@
         <v>4</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11">
         <v>4</v>
       </c>
       <c r="Q11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11">
         <v>5</v>
@@ -2649,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>6</v>
@@ -2667,7 +2667,7 @@
         <v>4</v>
       </c>
       <c r="AB11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -2684,10 +2684,10 @@
         <v>120</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -2699,13 +2699,13 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12">
         <v>4</v>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="S12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -2735,25 +2735,25 @@
         <v>5</v>
       </c>
       <c r="V12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>6</v>
       </c>
       <c r="X12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y12">
         <v>4</v>
       </c>
       <c r="Z12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA12">
         <v>4</v>
       </c>
       <c r="AB12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:28">
@@ -2773,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2782,7 +2782,7 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -2800,7 +2800,7 @@
         <v>3</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -2815,7 +2815,7 @@
         <v>6</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -2833,7 +2833,7 @@
         <v>3</v>
       </c>
       <c r="Z13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA13">
         <v>3</v>
@@ -2892,7 +2892,7 @@
         <v>5</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14">
         <v>3</v>
@@ -2916,10 +2916,10 @@
         <v>4</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA14">
         <v>3</v>
@@ -2942,16 +2942,16 @@
         <v>123</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>4</v>
@@ -2978,19 +2978,19 @@
         <v>5</v>
       </c>
       <c r="Q15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V15">
         <v>4</v>
@@ -3002,16 +3002,16 @@
         <v>2</v>
       </c>
       <c r="Y15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA15">
         <v>3</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:28">
@@ -3031,7 +3031,7 @@
         <v>4</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16">
         <v>4</v>
@@ -3049,7 +3049,7 @@
         <v>3</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M16">
         <v>3</v>
@@ -3114,10 +3114,10 @@
         <v>125</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17">
         <v>3</v>
@@ -3132,13 +3132,13 @@
         <v>3</v>
       </c>
       <c r="K17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>4</v>
       </c>
       <c r="M17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>4</v>
@@ -3183,7 +3183,7 @@
         <v>3</v>
       </c>
       <c r="AB17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:28">
@@ -3218,7 +3218,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>4</v>
@@ -3242,7 +3242,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>5</v>
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="AA18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB18">
         <v>1</v>
@@ -3322,7 +3322,7 @@
         <v>3</v>
       </c>
       <c r="Q19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>4</v>
@@ -3334,7 +3334,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V19">
         <v>4</v>
@@ -3372,7 +3372,7 @@
         <v>128</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>6</v>
@@ -3387,13 +3387,13 @@
         <v>3</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>5</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -3411,19 +3411,19 @@
         <v>6</v>
       </c>
       <c r="R20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>6</v>
       </c>
       <c r="T20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20">
         <v>6</v>
       </c>
       <c r="V20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -3461,13 +3461,13 @@
         <v>4</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21">
         <v>5</v>
@@ -3497,13 +3497,13 @@
         <v>5</v>
       </c>
       <c r="R21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>3</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>4</v>
@@ -3515,16 +3515,16 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB21">
         <v>3</v>
@@ -3669,13 +3669,13 @@
         <v>4</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S23">
         <v>4</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U23">
         <v>4</v>
@@ -3725,7 +3725,7 @@
         <v>4</v>
       </c>
       <c r="H24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24">
         <v>4</v>
@@ -3752,16 +3752,16 @@
         <v>3</v>
       </c>
       <c r="Q24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S24">
         <v>2</v>
       </c>
       <c r="T24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U24">
         <v>2</v>
@@ -3773,19 +3773,19 @@
         <v>6</v>
       </c>
       <c r="X24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24">
         <v>2</v>
       </c>
       <c r="Z24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA24">
         <v>2</v>
       </c>
       <c r="AB24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:28">
@@ -3838,22 +3838,22 @@
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S25">
         <v>6</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -3891,7 +3891,7 @@
         <v>4</v>
       </c>
       <c r="F26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -3927,7 +3927,7 @@
         <v>4</v>
       </c>
       <c r="R26">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>5</v>
@@ -3980,7 +3980,7 @@
         <v>5</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27">
         <v>4</v>
@@ -4016,7 +4016,7 @@
         <v>5</v>
       </c>
       <c r="S27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>4</v>
@@ -4072,7 +4072,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28">
         <v>4</v>
@@ -4090,7 +4090,7 @@
         <v>2</v>
       </c>
       <c r="O28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>6</v>
@@ -4102,25 +4102,25 @@
         <v>3</v>
       </c>
       <c r="S28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U28">
         <v>3</v>
       </c>
       <c r="V28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z28">
         <v>3</v>
@@ -4182,13 +4182,13 @@
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>3</v>
       </c>
       <c r="S29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T29">
         <v>3</v>
@@ -4203,7 +4203,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y29">
         <v>2</v>
@@ -4274,16 +4274,16 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U30">
         <v>6</v>
       </c>
       <c r="V30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -4339,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>6</v>
@@ -4490,7 +4490,7 @@
         <v>141</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33">
         <v>4</v>
@@ -4511,7 +4511,7 @@
         <v>3</v>
       </c>
       <c r="L33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M33">
         <v>3</v>
@@ -4553,13 +4553,13 @@
         <v>3</v>
       </c>
       <c r="Z33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA33">
         <v>2</v>
       </c>
       <c r="AB33">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:28">
@@ -4612,7 +4612,7 @@
         <v>5</v>
       </c>
       <c r="Q34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R34">
         <v>5</v>
@@ -4665,19 +4665,19 @@
         <v>4</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <v>4</v>
       </c>
       <c r="H35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I35">
         <v>4</v>
       </c>
       <c r="J35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K35">
         <v>5</v>
@@ -4689,13 +4689,13 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O35">
         <v>4</v>
       </c>
       <c r="P35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q35">
         <v>5</v>
@@ -4754,7 +4754,7 @@
         <v>3</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36">
         <v>4</v>
@@ -4790,7 +4790,7 @@
         <v>3</v>
       </c>
       <c r="S36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T36">
         <v>4</v>
@@ -4799,7 +4799,7 @@
         <v>4</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W36">
         <v>6</v>
@@ -4808,13 +4808,13 @@
         <v>4</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z36">
         <v>4</v>
       </c>
       <c r="AA36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB36">
         <v>5</v>
@@ -4846,7 +4846,7 @@
         <v>3</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -4855,7 +4855,7 @@
         <v>4</v>
       </c>
       <c r="L37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M37">
         <v>4</v>
@@ -4864,7 +4864,7 @@
         <v>4</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P37">
         <v>4</v>
@@ -4873,7 +4873,7 @@
         <v>6</v>
       </c>
       <c r="R37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S37">
         <v>4</v>
@@ -4894,7 +4894,7 @@
         <v>2</v>
       </c>
       <c r="Y37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z37">
         <v>1</v>
@@ -4956,22 +4956,22 @@
         <v>5</v>
       </c>
       <c r="Q38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W38">
         <v>6</v>
@@ -4986,7 +4986,7 @@
         <v>3</v>
       </c>
       <c r="AA38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB38">
         <v>2</v>
@@ -5024,7 +5024,7 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L39">
         <v>4</v>
@@ -5045,7 +5045,7 @@
         <v>7</v>
       </c>
       <c r="R39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S39">
         <v>7</v>
@@ -5069,13 +5069,13 @@
         <v>2</v>
       </c>
       <c r="Z39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA39">
         <v>2</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:28">
@@ -5199,7 +5199,7 @@
         <v>4</v>
       </c>
       <c r="L41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41">
         <v>3</v>
@@ -5241,13 +5241,13 @@
         <v>4</v>
       </c>
       <c r="Z41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:28">
@@ -5267,7 +5267,7 @@
         <v>6</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G42">
         <v>4</v>
@@ -5309,7 +5309,7 @@
         <v>5</v>
       </c>
       <c r="T42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>6</v>
@@ -5324,10 +5324,10 @@
         <v>2</v>
       </c>
       <c r="Y42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA42">
         <v>2</v>
@@ -5350,7 +5350,7 @@
         <v>151</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43">
         <v>4</v>
@@ -5365,7 +5365,7 @@
         <v>4</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>4</v>
@@ -5389,13 +5389,13 @@
         <v>6</v>
       </c>
       <c r="R43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S43">
         <v>6</v>
       </c>
       <c r="T43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>4</v>
@@ -5416,7 +5416,7 @@
         <v>2</v>
       </c>
       <c r="AA43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB43">
         <v>3</v>
@@ -5457,7 +5457,7 @@
         <v>4</v>
       </c>
       <c r="L44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44">
         <v>4</v>
@@ -5475,16 +5475,16 @@
         <v>4</v>
       </c>
       <c r="R44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T44">
         <v>4</v>
       </c>
       <c r="U44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V44">
         <v>3</v>
@@ -5493,13 +5493,13 @@
         <v>6</v>
       </c>
       <c r="X44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y44">
         <v>3</v>
       </c>
       <c r="Z44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA44">
         <v>2</v>
@@ -5537,7 +5537,7 @@
         <v>4</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45">
         <v>5</v>
@@ -5582,7 +5582,7 @@
         <v>2</v>
       </c>
       <c r="Y45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z45">
         <v>2</v>
@@ -5591,7 +5591,7 @@
         <v>2</v>
       </c>
       <c r="AB45">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:28">
@@ -5644,7 +5644,7 @@
         <v>6</v>
       </c>
       <c r="Q46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R46">
         <v>5</v>
@@ -5668,7 +5668,7 @@
         <v>2</v>
       </c>
       <c r="Y46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46">
         <v>3</v>
@@ -5697,10 +5697,10 @@
         <v>4</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H47">
         <v>3</v>
@@ -5721,16 +5721,16 @@
         <v>4</v>
       </c>
       <c r="N47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O47">
         <v>2</v>
       </c>
       <c r="P47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R47">
         <v>6</v>
@@ -5751,19 +5751,19 @@
         <v>6</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z47">
         <v>2</v>
       </c>
       <c r="AA47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:28">
@@ -5866,7 +5866,7 @@
         <v>157</v>
       </c>
       <c r="E49">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F49">
         <v>4</v>
@@ -5884,7 +5884,7 @@
         <v>4</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -5932,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="AA49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB49">
         <v>1</v>
@@ -5991,7 +5991,7 @@
         <v>7</v>
       </c>
       <c r="R50">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S50">
         <v>6</v>
@@ -6000,7 +6000,7 @@
         <v>7</v>
       </c>
       <c r="U50">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V50">
         <v>6</v>
@@ -6101,10 +6101,10 @@
         <v>4</v>
       </c>
       <c r="Z51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB51">
         <v>4</v>
@@ -6246,7 +6246,7 @@
         <v>3</v>
       </c>
       <c r="Q53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R53">
         <v>7</v>
@@ -6356,7 +6356,7 @@
         <v>2</v>
       </c>
       <c r="Y54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z54">
         <v>3</v>
@@ -6382,7 +6382,7 @@
         <v>163</v>
       </c>
       <c r="E55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F55">
         <v>4</v>
@@ -6448,7 +6448,7 @@
         <v>4</v>
       </c>
       <c r="AA55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB55">
         <v>3</v>
@@ -6468,7 +6468,7 @@
         <v>164</v>
       </c>
       <c r="E56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F56">
         <v>6</v>
@@ -6599,7 +6599,7 @@
         <v>5</v>
       </c>
       <c r="T57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U57">
         <v>6</v>
@@ -6652,7 +6652,7 @@
         <v>5</v>
       </c>
       <c r="I58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J58">
         <v>5</v>
@@ -6670,7 +6670,7 @@
         <v>2</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P58">
         <v>6</v>
@@ -6682,7 +6682,7 @@
         <v>7</v>
       </c>
       <c r="S58">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T58">
         <v>6</v>
@@ -6706,7 +6706,7 @@
         <v>2</v>
       </c>
       <c r="AA58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB58">
         <v>2</v>
@@ -6765,10 +6765,10 @@
         <v>5</v>
       </c>
       <c r="R59">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T59">
         <v>5</v>
@@ -6795,7 +6795,7 @@
         <v>3</v>
       </c>
       <c r="AB59">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:28">
@@ -6827,7 +6827,7 @@
         <v>2</v>
       </c>
       <c r="J60">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K60">
         <v>5</v>
@@ -6901,7 +6901,7 @@
         <v>3</v>
       </c>
       <c r="F61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G61">
         <v>2</v>
@@ -6916,13 +6916,13 @@
         <v>3</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L61">
         <v>3</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61">
         <v>5</v>
@@ -6940,7 +6940,7 @@
         <v>4</v>
       </c>
       <c r="S61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T61">
         <v>4</v>
@@ -6949,7 +6949,7 @@
         <v>5</v>
       </c>
       <c r="V61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W61">
         <v>6</v>
@@ -6958,13 +6958,13 @@
         <v>3</v>
       </c>
       <c r="Y61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z61">
         <v>3</v>
       </c>
       <c r="AA61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB61">
         <v>4</v>
@@ -6984,7 +6984,7 @@
         <v>170</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62">
         <v>5</v>
@@ -7020,7 +7020,7 @@
         <v>5</v>
       </c>
       <c r="Q62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R62">
         <v>5</v>
@@ -7029,13 +7029,13 @@
         <v>4</v>
       </c>
       <c r="T62">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U62">
         <v>5</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W62">
         <v>6</v>
@@ -7044,13 +7044,13 @@
         <v>3</v>
       </c>
       <c r="Y62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB62">
         <v>3</v>
@@ -7127,7 +7127,7 @@
         <v>6</v>
       </c>
       <c r="X63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y63">
         <v>5</v>
@@ -7136,7 +7136,7 @@
         <v>4</v>
       </c>
       <c r="AA63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB63">
         <v>5</v>
@@ -7201,10 +7201,10 @@
         <v>4</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U64">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V64">
         <v>5</v>
@@ -7340,7 +7340,7 @@
         <v>6</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66">
         <v>5</v>
@@ -7358,7 +7358,7 @@
         <v>3</v>
       </c>
       <c r="O66">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P66">
         <v>5</v>
@@ -7373,7 +7373,7 @@
         <v>7</v>
       </c>
       <c r="T66">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U66">
         <v>7</v>
@@ -7391,13 +7391,13 @@
         <v>2</v>
       </c>
       <c r="Z66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA66">
         <v>2</v>
       </c>
       <c r="AB66">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:28">
@@ -7414,7 +7414,7 @@
         <v>175</v>
       </c>
       <c r="E67">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -7438,7 +7438,7 @@
         <v>5</v>
       </c>
       <c r="M67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N67">
         <v>3</v>
@@ -7462,7 +7462,7 @@
         <v>4</v>
       </c>
       <c r="U67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V67">
         <v>3</v>
@@ -7551,13 +7551,13 @@
         <v>5</v>
       </c>
       <c r="V68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W68">
         <v>6</v>
       </c>
       <c r="X68">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y68">
         <v>4</v>
@@ -7566,7 +7566,7 @@
         <v>3</v>
       </c>
       <c r="AA68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB68">
         <v>5</v>
@@ -7586,7 +7586,7 @@
         <v>177</v>
       </c>
       <c r="E69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F69">
         <v>4</v>
@@ -7607,7 +7607,7 @@
         <v>5</v>
       </c>
       <c r="L69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M69">
         <v>5</v>
@@ -7646,7 +7646,7 @@
         <v>2</v>
       </c>
       <c r="Y69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z69">
         <v>2</v>
@@ -7687,7 +7687,7 @@
         <v>3</v>
       </c>
       <c r="J70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K70">
         <v>4</v>
@@ -7708,22 +7708,22 @@
         <v>4</v>
       </c>
       <c r="Q70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S70">
         <v>7</v>
       </c>
       <c r="T70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U70">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V70">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W70">
         <v>6</v>
@@ -7735,13 +7735,13 @@
         <v>2</v>
       </c>
       <c r="Z70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA70">
         <v>2</v>
       </c>
       <c r="AB70">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:28">
@@ -7844,13 +7844,13 @@
         <v>180</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F72">
         <v>4</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H72">
         <v>4</v>
@@ -7862,10 +7862,10 @@
         <v>5</v>
       </c>
       <c r="K72">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M72">
         <v>3</v>
@@ -7880,22 +7880,22 @@
         <v>5</v>
       </c>
       <c r="Q72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S72">
         <v>4</v>
       </c>
       <c r="T72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U72">
         <v>3</v>
       </c>
       <c r="V72">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W72">
         <v>6</v>
@@ -7904,16 +7904,16 @@
         <v>3</v>
       </c>
       <c r="Y72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB72">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:28">
@@ -7936,7 +7936,7 @@
         <v>5</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H73">
         <v>6</v>
@@ -7996,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="AA73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB73">
         <v>1</v>
@@ -8102,7 +8102,7 @@
         <v>183</v>
       </c>
       <c r="E75">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F75">
         <v>7</v>
@@ -8111,7 +8111,7 @@
         <v>7</v>
       </c>
       <c r="H75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -8194,7 +8194,7 @@
         <v>4</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H76">
         <v>3</v>
@@ -8212,7 +8212,7 @@
         <v>3</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N76">
         <v>3</v>
@@ -8230,10 +8230,10 @@
         <v>3</v>
       </c>
       <c r="S76">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U76">
         <v>4</v>
@@ -8245,10 +8245,10 @@
         <v>6</v>
       </c>
       <c r="X76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z76">
         <v>2</v>
@@ -8257,7 +8257,7 @@
         <v>1</v>
       </c>
       <c r="AB76">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:28">
@@ -8286,7 +8286,7 @@
         <v>6</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J77">
         <v>3</v>
@@ -8304,7 +8304,7 @@
         <v>4</v>
       </c>
       <c r="O77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P77">
         <v>4</v>
@@ -8396,7 +8396,7 @@
         <v>5</v>
       </c>
       <c r="Q78">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R78">
         <v>5</v>
@@ -8458,7 +8458,7 @@
         <v>5</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J79">
         <v>5</v>
@@ -8476,7 +8476,7 @@
         <v>4</v>
       </c>
       <c r="O79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P79">
         <v>4</v>
@@ -8485,7 +8485,7 @@
         <v>5</v>
       </c>
       <c r="R79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S79">
         <v>5</v>
@@ -8497,13 +8497,13 @@
         <v>4</v>
       </c>
       <c r="V79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W79">
         <v>6</v>
       </c>
       <c r="X79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y79">
         <v>4</v>
@@ -8571,7 +8571,7 @@
         <v>6</v>
       </c>
       <c r="R80">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S80">
         <v>6</v>
@@ -8598,7 +8598,7 @@
         <v>2</v>
       </c>
       <c r="AA80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB80">
         <v>1</v>
@@ -8630,7 +8630,7 @@
         <v>4</v>
       </c>
       <c r="I81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J81">
         <v>5</v>
@@ -8648,7 +8648,7 @@
         <v>3</v>
       </c>
       <c r="O81">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P81">
         <v>5</v>
@@ -8728,7 +8728,7 @@
         <v>5</v>
       </c>
       <c r="M82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N82">
         <v>3</v>
@@ -8746,13 +8746,13 @@
         <v>6</v>
       </c>
       <c r="S82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T82">
         <v>4</v>
       </c>
       <c r="U82">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V82">
         <v>5</v>
@@ -8835,7 +8835,7 @@
         <v>4</v>
       </c>
       <c r="T83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U83">
         <v>4</v>
@@ -8847,7 +8847,7 @@
         <v>6</v>
       </c>
       <c r="X83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y83">
         <v>4</v>
@@ -8879,7 +8879,7 @@
         <v>4</v>
       </c>
       <c r="F84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G84">
         <v>4</v>
@@ -8894,10 +8894,10 @@
         <v>4</v>
       </c>
       <c r="K84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L84">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M84">
         <v>4</v>
@@ -8915,7 +8915,7 @@
         <v>2</v>
       </c>
       <c r="R84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S84">
         <v>2</v>
@@ -8924,7 +8924,7 @@
         <v>3</v>
       </c>
       <c r="U84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V84">
         <v>3</v>
@@ -8942,7 +8942,7 @@
         <v>5</v>
       </c>
       <c r="AA84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB84">
         <v>4</v>
@@ -8989,13 +8989,13 @@
         <v>6</v>
       </c>
       <c r="N85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O85">
         <v>6</v>
       </c>
       <c r="P85">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q85">
         <v>7</v>
@@ -9096,10 +9096,10 @@
         <v>3</v>
       </c>
       <c r="U86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W86">
         <v>6</v>
@@ -9108,16 +9108,16 @@
         <v>4</v>
       </c>
       <c r="Y86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB86">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:28">
@@ -9158,7 +9158,7 @@
         <v>5</v>
       </c>
       <c r="M87">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N87">
         <v>3</v>
@@ -9179,7 +9179,7 @@
         <v>5</v>
       </c>
       <c r="T87">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U87">
         <v>5</v>
@@ -9197,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="Z87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA87">
         <v>3</v>
@@ -9229,7 +9229,7 @@
         <v>3</v>
       </c>
       <c r="H88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I88">
         <v>5</v>
@@ -9259,7 +9259,7 @@
         <v>5</v>
       </c>
       <c r="R88">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S88">
         <v>5</v>
@@ -9268,7 +9268,7 @@
         <v>5</v>
       </c>
       <c r="U88">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V88">
         <v>5</v>
@@ -9437,7 +9437,7 @@
         <v>5</v>
       </c>
       <c r="T90">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U90">
         <v>4</v>
@@ -9452,7 +9452,7 @@
         <v>3</v>
       </c>
       <c r="Y90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z90">
         <v>2</v>
@@ -9481,7 +9481,7 @@
         <v>4</v>
       </c>
       <c r="F91">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G91">
         <v>4</v>
@@ -9585,7 +9585,7 @@
         <v>5</v>
       </c>
       <c r="L92">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M92">
         <v>5</v>
@@ -9612,7 +9612,7 @@
         <v>7</v>
       </c>
       <c r="U92">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V92">
         <v>6</v>
@@ -9624,7 +9624,7 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z92">
         <v>2</v>
@@ -9686,13 +9686,13 @@
         <v>3</v>
       </c>
       <c r="Q93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R93">
         <v>4</v>
       </c>
       <c r="S93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T93">
         <v>3</v>
@@ -9707,7 +9707,7 @@
         <v>6</v>
       </c>
       <c r="X93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y93">
         <v>6</v>
@@ -9719,7 +9719,7 @@
         <v>5</v>
       </c>
       <c r="AB93">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:28">
@@ -9739,7 +9739,7 @@
         <v>4</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94">
         <v>4</v>
@@ -9748,7 +9748,7 @@
         <v>3</v>
       </c>
       <c r="I94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J94">
         <v>3</v>
@@ -9766,7 +9766,7 @@
         <v>5</v>
       </c>
       <c r="O94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P94">
         <v>3</v>
@@ -9787,7 +9787,7 @@
         <v>3</v>
       </c>
       <c r="V94">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W94">
         <v>6</v>
@@ -9802,10 +9802,10 @@
         <v>3</v>
       </c>
       <c r="AA94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB94">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:28">
@@ -9828,10 +9828,10 @@
         <v>5</v>
       </c>
       <c r="G95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I95">
         <v>4</v>
@@ -9840,7 +9840,7 @@
         <v>6</v>
       </c>
       <c r="K95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L95">
         <v>5</v>
@@ -9861,10 +9861,10 @@
         <v>4</v>
       </c>
       <c r="R95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S95">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T95">
         <v>4</v>
@@ -9885,7 +9885,7 @@
         <v>5</v>
       </c>
       <c r="Z95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA95">
         <v>4</v>
@@ -9932,7 +9932,7 @@
         <v>6</v>
       </c>
       <c r="M96">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -9965,10 +9965,10 @@
         <v>6</v>
       </c>
       <c r="X96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y96">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z96">
         <v>3</v>
@@ -9977,7 +9977,7 @@
         <v>2</v>
       </c>
       <c r="AB96">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97" spans="1:28">
@@ -10039,7 +10039,7 @@
         <v>4</v>
       </c>
       <c r="T97">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U97">
         <v>5</v>
@@ -10051,7 +10051,7 @@
         <v>6</v>
       </c>
       <c r="X97">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y97">
         <v>4</v>
@@ -10080,7 +10080,7 @@
         <v>206</v>
       </c>
       <c r="E98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F98">
         <v>6</v>
@@ -10101,7 +10101,7 @@
         <v>4</v>
       </c>
       <c r="L98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M98">
         <v>5</v>
@@ -10119,13 +10119,13 @@
         <v>5</v>
       </c>
       <c r="R98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U98">
         <v>4</v>
@@ -10146,7 +10146,7 @@
         <v>1</v>
       </c>
       <c r="AA98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB98">
         <v>1</v>
@@ -10172,7 +10172,7 @@
         <v>4</v>
       </c>
       <c r="G99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H99">
         <v>3</v>
@@ -10214,7 +10214,7 @@
         <v>2</v>
       </c>
       <c r="U99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V99">
         <v>3</v>
@@ -10267,13 +10267,13 @@
         <v>4</v>
       </c>
       <c r="J100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K100">
         <v>4</v>
       </c>
       <c r="L100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M100">
         <v>3</v>
@@ -10288,7 +10288,7 @@
         <v>3</v>
       </c>
       <c r="Q100">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R100">
         <v>3</v>
@@ -10303,7 +10303,7 @@
         <v>2</v>
       </c>
       <c r="V100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W100">
         <v>6</v>
@@ -10321,7 +10321,7 @@
         <v>3</v>
       </c>
       <c r="AB100">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:28">
@@ -10377,16 +10377,16 @@
         <v>3</v>
       </c>
       <c r="R101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T101">
         <v>3</v>
       </c>
       <c r="U101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V101">
         <v>2</v>
@@ -10469,19 +10469,19 @@
         <v>4</v>
       </c>
       <c r="T102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U102">
         <v>7</v>
       </c>
       <c r="V102">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W102">
         <v>6</v>
       </c>
       <c r="X102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y102">
         <v>1</v>
@@ -10493,7 +10493,7 @@
         <v>3</v>
       </c>
       <c r="AB102">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:28">
@@ -10546,13 +10546,13 @@
         <v>3</v>
       </c>
       <c r="Q103">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T103">
         <v>4</v>
@@ -10567,16 +10567,16 @@
         <v>6</v>
       </c>
       <c r="X103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y103">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z103">
         <v>4</v>
       </c>
       <c r="AA103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB103">
         <v>5</v>
@@ -10602,7 +10602,7 @@
         <v>5</v>
       </c>
       <c r="G104">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H104">
         <v>4</v>
@@ -10623,13 +10623,13 @@
         <v>4</v>
       </c>
       <c r="N104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O104">
         <v>4</v>
       </c>
       <c r="P104">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q104">
         <v>6</v>
@@ -10685,7 +10685,7 @@
         <v>4</v>
       </c>
       <c r="F105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G105">
         <v>5</v>
@@ -10706,22 +10706,22 @@
         <v>4</v>
       </c>
       <c r="M105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O105">
         <v>4</v>
       </c>
       <c r="P105">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q105">
         <v>4</v>
       </c>
       <c r="R105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S105">
         <v>6</v>
@@ -10768,7 +10768,7 @@
         <v>214</v>
       </c>
       <c r="E106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F106">
         <v>3</v>
@@ -10792,7 +10792,7 @@
         <v>4</v>
       </c>
       <c r="M106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N106">
         <v>5</v>
@@ -10854,7 +10854,7 @@
         <v>215</v>
       </c>
       <c r="E107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F107">
         <v>4</v>
@@ -10869,13 +10869,13 @@
         <v>5</v>
       </c>
       <c r="J107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M107">
         <v>4</v>
@@ -10893,28 +10893,28 @@
         <v>5</v>
       </c>
       <c r="R107">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T107">
         <v>6</v>
       </c>
       <c r="U107">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V107">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W107">
         <v>6</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y107">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z107">
         <v>3</v>
@@ -10923,7 +10923,7 @@
         <v>2</v>
       </c>
       <c r="AB107">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:28">
@@ -10946,7 +10946,7 @@
         <v>6</v>
       </c>
       <c r="G108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H108">
         <v>4</v>
@@ -11089,7 +11089,7 @@
         <v>2</v>
       </c>
       <c r="Z109">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA109">
         <v>3</v>
@@ -11118,16 +11118,16 @@
         <v>5</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I110">
         <v>2</v>
       </c>
       <c r="J110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K110">
         <v>5</v>
@@ -11154,16 +11154,16 @@
         <v>4</v>
       </c>
       <c r="S110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U110">
         <v>4</v>
       </c>
       <c r="V110">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W110">
         <v>6</v>
@@ -11172,16 +11172,16 @@
         <v>4</v>
       </c>
       <c r="Y110">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA110">
         <v>5</v>
       </c>
       <c r="AB110">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:28">
@@ -11207,7 +11207,7 @@
         <v>4</v>
       </c>
       <c r="H111">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I111">
         <v>5</v>
@@ -11237,7 +11237,7 @@
         <v>5</v>
       </c>
       <c r="R111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S111">
         <v>4</v>
@@ -11284,7 +11284,7 @@
         <v>220</v>
       </c>
       <c r="E112">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F112">
         <v>4</v>
@@ -11394,22 +11394,22 @@
         <v>3</v>
       </c>
       <c r="M113">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O113">
         <v>4</v>
       </c>
       <c r="P113">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q113">
         <v>2</v>
       </c>
       <c r="R113">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S113">
         <v>4</v>
@@ -11495,10 +11495,10 @@
         <v>4</v>
       </c>
       <c r="R114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S114">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T114">
         <v>5</v>
@@ -11513,13 +11513,13 @@
         <v>6</v>
       </c>
       <c r="X114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y114">
         <v>1</v>
       </c>
       <c r="Z114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA114">
         <v>2</v>
@@ -11602,7 +11602,7 @@
         <v>1</v>
       </c>
       <c r="Y115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z115">
         <v>3</v>
@@ -11670,7 +11670,7 @@
         <v>5</v>
       </c>
       <c r="S116">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T116">
         <v>5</v>
@@ -11723,7 +11723,7 @@
         <v>4</v>
       </c>
       <c r="H117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I117">
         <v>4</v>
@@ -11753,10 +11753,10 @@
         <v>2</v>
       </c>
       <c r="R117">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S117">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T117">
         <v>2</v>
@@ -11765,7 +11765,7 @@
         <v>2</v>
       </c>
       <c r="V117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W117">
         <v>6</v>
@@ -11818,13 +11818,13 @@
         <v>5</v>
       </c>
       <c r="K118">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L118">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N118">
         <v>3</v>
@@ -11860,7 +11860,7 @@
         <v>4</v>
       </c>
       <c r="Y118">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z118">
         <v>4</v>
@@ -11886,10 +11886,10 @@
         <v>227</v>
       </c>
       <c r="E119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F119">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G119">
         <v>4</v>
@@ -11898,7 +11898,7 @@
         <v>7</v>
       </c>
       <c r="I119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J119">
         <v>5</v>
@@ -11916,7 +11916,7 @@
         <v>2</v>
       </c>
       <c r="O119">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P119">
         <v>6</v>
@@ -11949,7 +11949,7 @@
         <v>1</v>
       </c>
       <c r="Z119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA119">
         <v>1</v>
@@ -11978,7 +11978,7 @@
         <v>5</v>
       </c>
       <c r="G120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H120">
         <v>5</v>
@@ -12097,7 +12097,7 @@
         <v>6</v>
       </c>
       <c r="R121">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S121">
         <v>5</v>
@@ -12183,19 +12183,19 @@
         <v>2</v>
       </c>
       <c r="R122">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U122">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W122">
         <v>6</v>
@@ -12239,7 +12239,7 @@
         <v>5</v>
       </c>
       <c r="H123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I123">
         <v>2</v>
@@ -12248,10 +12248,10 @@
         <v>6</v>
       </c>
       <c r="K123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L123">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M123">
         <v>5</v>
@@ -12290,7 +12290,7 @@
         <v>3</v>
       </c>
       <c r="Y123">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z123">
         <v>3</v>
@@ -12355,10 +12355,10 @@
         <v>5</v>
       </c>
       <c r="R124">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S124">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T124">
         <v>5</v>
@@ -12376,16 +12376,16 @@
         <v>1</v>
       </c>
       <c r="Y124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z124">
         <v>1</v>
       </c>
       <c r="AA124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB124">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:28">
@@ -12405,10 +12405,10 @@
         <v>5</v>
       </c>
       <c r="F125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H125">
         <v>3</v>
@@ -12459,7 +12459,7 @@
         <v>6</v>
       </c>
       <c r="X125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y125">
         <v>3</v>
@@ -12468,7 +12468,7 @@
         <v>3</v>
       </c>
       <c r="AA125">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB125">
         <v>4</v>
@@ -12524,37 +12524,37 @@
         <v>3</v>
       </c>
       <c r="Q126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U126">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W126">
         <v>6</v>
       </c>
       <c r="X126">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y126">
         <v>3</v>
       </c>
       <c r="Z126">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB126">
         <v>4</v>
@@ -12580,7 +12580,7 @@
         <v>5</v>
       </c>
       <c r="G127">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H127">
         <v>5</v>
@@ -12598,7 +12598,7 @@
         <v>5</v>
       </c>
       <c r="M127">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N127">
         <v>3</v>
@@ -12610,7 +12610,7 @@
         <v>5</v>
       </c>
       <c r="Q127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R127">
         <v>6</v>
@@ -12625,7 +12625,7 @@
         <v>6</v>
       </c>
       <c r="V127">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W127">
         <v>6</v>
@@ -12666,7 +12666,7 @@
         <v>5</v>
       </c>
       <c r="G128">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H128">
         <v>5</v>
@@ -12696,7 +12696,7 @@
         <v>4</v>
       </c>
       <c r="Q128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R128">
         <v>7</v>
@@ -12726,7 +12726,7 @@
         <v>2</v>
       </c>
       <c r="AA128">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB128">
         <v>1</v>
@@ -12749,13 +12749,13 @@
         <v>5</v>
       </c>
       <c r="F129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G129">
         <v>4</v>
       </c>
       <c r="H129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I129">
         <v>3</v>
@@ -12770,7 +12770,7 @@
         <v>4</v>
       </c>
       <c r="M129">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N129">
         <v>4</v>
@@ -12806,7 +12806,7 @@
         <v>3</v>
       </c>
       <c r="Y129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z129">
         <v>2</v>
@@ -12841,7 +12841,7 @@
         <v>5</v>
       </c>
       <c r="H130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I130">
         <v>3</v>
@@ -12874,13 +12874,13 @@
         <v>6</v>
       </c>
       <c r="S130">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T130">
         <v>5</v>
       </c>
       <c r="U130">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V130">
         <v>6</v>
@@ -13043,7 +13043,7 @@
         <v>3</v>
       </c>
       <c r="R132">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S132">
         <v>4</v>
@@ -13055,25 +13055,25 @@
         <v>4</v>
       </c>
       <c r="V132">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W132">
         <v>6</v>
       </c>
       <c r="X132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y132">
         <v>2</v>
       </c>
       <c r="Z132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA132">
         <v>2</v>
       </c>
       <c r="AB132">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:28">
@@ -13105,7 +13105,7 @@
         <v>3</v>
       </c>
       <c r="J133">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K133">
         <v>5</v>
@@ -13138,7 +13138,7 @@
         <v>5</v>
       </c>
       <c r="U133">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V133">
         <v>4</v>
@@ -13218,7 +13218,7 @@
         <v>4</v>
       </c>
       <c r="S134">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T134">
         <v>4</v>
@@ -13351,7 +13351,7 @@
         <v>4</v>
       </c>
       <c r="F136">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G136">
         <v>4</v>
@@ -13372,7 +13372,7 @@
         <v>5</v>
       </c>
       <c r="M136">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N136">
         <v>3</v>
@@ -13437,13 +13437,13 @@
         <v>6</v>
       </c>
       <c r="F137">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G137">
         <v>5</v>
       </c>
       <c r="H137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I137">
         <v>3</v>
@@ -13461,28 +13461,28 @@
         <v>5</v>
       </c>
       <c r="N137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O137">
         <v>5</v>
       </c>
       <c r="P137">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R137">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S137">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V137">
         <v>6</v>
@@ -13491,16 +13491,16 @@
         <v>6</v>
       </c>
       <c r="X137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y137">
         <v>4</v>
       </c>
       <c r="Z137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA137">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB137">
         <v>3</v>
@@ -13556,16 +13556,16 @@
         <v>4</v>
       </c>
       <c r="Q138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R138">
         <v>3</v>
       </c>
       <c r="S138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T138">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U138">
         <v>2</v>
@@ -13586,7 +13586,7 @@
         <v>4</v>
       </c>
       <c r="AA138">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB138">
         <v>4</v>
@@ -13618,7 +13618,7 @@
         <v>5</v>
       </c>
       <c r="I139">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J139">
         <v>5</v>
@@ -13636,7 +13636,7 @@
         <v>2</v>
       </c>
       <c r="O139">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P139">
         <v>6</v>
@@ -13648,10 +13648,10 @@
         <v>6</v>
       </c>
       <c r="S139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T139">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U139">
         <v>6</v>
@@ -13666,16 +13666,16 @@
         <v>3</v>
       </c>
       <c r="Y139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z139">
         <v>2</v>
       </c>
       <c r="AA139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB139">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:28">
@@ -13701,16 +13701,16 @@
         <v>4</v>
       </c>
       <c r="H140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I140">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L140">
         <v>4</v>
@@ -13722,7 +13722,7 @@
         <v>3</v>
       </c>
       <c r="O140">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P140">
         <v>5</v>
@@ -13740,10 +13740,10 @@
         <v>5</v>
       </c>
       <c r="U140">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V140">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W140">
         <v>6</v>
@@ -13752,10 +13752,10 @@
         <v>3</v>
       </c>
       <c r="Y140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z140">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA140">
         <v>2</v>
@@ -13817,16 +13817,16 @@
         <v>3</v>
       </c>
       <c r="R141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S141">
         <v>3</v>
       </c>
       <c r="T141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V141">
         <v>2</v>
@@ -13835,7 +13835,7 @@
         <v>6</v>
       </c>
       <c r="X141">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y141">
         <v>3</v>
@@ -13867,7 +13867,7 @@
         <v>5</v>
       </c>
       <c r="F142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G142">
         <v>5</v>
@@ -13882,7 +13882,7 @@
         <v>4</v>
       </c>
       <c r="K142">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L142">
         <v>4</v>
@@ -13903,13 +13903,13 @@
         <v>7</v>
       </c>
       <c r="R142">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S142">
         <v>6</v>
       </c>
       <c r="T142">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U142">
         <v>7</v>
@@ -13930,7 +13930,7 @@
         <v>1</v>
       </c>
       <c r="AA142">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB142">
         <v>2</v>
@@ -13956,7 +13956,7 @@
         <v>5</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H143">
         <v>5</v>
@@ -14001,7 +14001,7 @@
         <v>4</v>
       </c>
       <c r="V143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W143">
         <v>6</v>
@@ -14036,7 +14036,7 @@
         <v>252</v>
       </c>
       <c r="E144">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F144">
         <v>4</v>
@@ -14048,7 +14048,7 @@
         <v>5</v>
       </c>
       <c r="I144">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J144">
         <v>4</v>
@@ -14066,7 +14066,7 @@
         <v>3</v>
       </c>
       <c r="O144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P144">
         <v>5</v>
@@ -14081,7 +14081,7 @@
         <v>3</v>
       </c>
       <c r="T144">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U144">
         <v>4</v>
@@ -14102,7 +14102,7 @@
         <v>3</v>
       </c>
       <c r="AA144">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB144">
         <v>2</v>
@@ -14122,7 +14122,7 @@
         <v>253</v>
       </c>
       <c r="E145">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F145">
         <v>4</v>
@@ -14208,7 +14208,7 @@
         <v>254</v>
       </c>
       <c r="E146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F146">
         <v>5</v>
@@ -14247,19 +14247,19 @@
         <v>4</v>
       </c>
       <c r="R146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T146">
         <v>5</v>
       </c>
       <c r="U146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W146">
         <v>6</v>
@@ -14277,7 +14277,7 @@
         <v>3</v>
       </c>
       <c r="AB146">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147" spans="1:28">
@@ -14351,7 +14351,7 @@
         <v>6</v>
       </c>
       <c r="X147">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y147">
         <v>1</v>
@@ -14380,13 +14380,13 @@
         <v>256</v>
       </c>
       <c r="E148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H148">
         <v>5</v>
@@ -14395,7 +14395,7 @@
         <v>3</v>
       </c>
       <c r="J148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K148">
         <v>6</v>
@@ -14404,7 +14404,7 @@
         <v>4</v>
       </c>
       <c r="M148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N148">
         <v>3</v>
@@ -14416,10 +14416,10 @@
         <v>5</v>
       </c>
       <c r="Q148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S148">
         <v>5</v>
@@ -14440,16 +14440,16 @@
         <v>5</v>
       </c>
       <c r="Y148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA148">
         <v>4</v>
       </c>
       <c r="AB148">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:28">
@@ -14517,7 +14517,7 @@
         <v>5</v>
       </c>
       <c r="V149">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W149">
         <v>6</v>
@@ -14532,7 +14532,7 @@
         <v>2</v>
       </c>
       <c r="AA149">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB149">
         <v>3</v>
@@ -14561,13 +14561,13 @@
         <v>3</v>
       </c>
       <c r="H150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I150">
         <v>5</v>
       </c>
       <c r="J150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K150">
         <v>3</v>
@@ -14576,7 +14576,7 @@
         <v>3</v>
       </c>
       <c r="M150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N150">
         <v>5</v>
@@ -14594,7 +14594,7 @@
         <v>4</v>
       </c>
       <c r="S150">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T150">
         <v>3</v>
@@ -14609,19 +14609,19 @@
         <v>6</v>
       </c>
       <c r="X150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z150">
         <v>2</v>
       </c>
       <c r="AA150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB150">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:28">
@@ -14686,7 +14686,7 @@
         <v>6</v>
       </c>
       <c r="U151">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V151">
         <v>5</v>
@@ -14760,7 +14760,7 @@
         <v>6</v>
       </c>
       <c r="Q152">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R152">
         <v>5</v>
@@ -14772,7 +14772,7 @@
         <v>5</v>
       </c>
       <c r="U152">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V152">
         <v>6</v>
@@ -14784,7 +14784,7 @@
         <v>4</v>
       </c>
       <c r="Y152">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z152">
         <v>4</v>
@@ -14816,7 +14816,7 @@
         <v>5</v>
       </c>
       <c r="G153">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H153">
         <v>6</v>
@@ -14825,7 +14825,7 @@
         <v>3</v>
       </c>
       <c r="J153">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K153">
         <v>4</v>
@@ -14846,13 +14846,13 @@
         <v>4</v>
       </c>
       <c r="Q153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R153">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S153">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T153">
         <v>3</v>
@@ -14896,7 +14896,7 @@
         <v>262</v>
       </c>
       <c r="E154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F154">
         <v>4</v>
@@ -14905,10 +14905,10 @@
         <v>5</v>
       </c>
       <c r="H154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J154">
         <v>5</v>
@@ -14917,7 +14917,7 @@
         <v>5</v>
       </c>
       <c r="L154">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M154">
         <v>4</v>
@@ -14926,7 +14926,7 @@
         <v>3</v>
       </c>
       <c r="O154">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P154">
         <v>5</v>
@@ -14935,10 +14935,10 @@
         <v>7</v>
       </c>
       <c r="R154">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S154">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T154">
         <v>7</v>
@@ -14947,13 +14947,13 @@
         <v>6</v>
       </c>
       <c r="V154">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W154">
         <v>6</v>
       </c>
       <c r="X154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y154">
         <v>3</v>
@@ -14962,10 +14962,10 @@
         <v>2</v>
       </c>
       <c r="AA154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB154">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:28">
@@ -14997,7 +14997,7 @@
         <v>3</v>
       </c>
       <c r="J155">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K155">
         <v>6</v>
@@ -15243,7 +15243,7 @@
         <v>5</v>
       </c>
       <c r="F158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G158">
         <v>5</v>
@@ -15252,7 +15252,7 @@
         <v>5</v>
       </c>
       <c r="I158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J158">
         <v>5</v>
@@ -15261,55 +15261,55 @@
         <v>6</v>
       </c>
       <c r="L158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S158">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U158">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V158">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W158">
         <v>6</v>
       </c>
       <c r="X158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y158">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z158">
         <v>6</v>
       </c>
       <c r="AA158">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB158">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:28">
@@ -15362,13 +15362,13 @@
         <v>5</v>
       </c>
       <c r="Q159">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R159">
         <v>5</v>
       </c>
       <c r="S159">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T159">
         <v>5</v>
@@ -15377,7 +15377,7 @@
         <v>5</v>
       </c>
       <c r="V159">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W159">
         <v>6</v>
@@ -15389,7 +15389,7 @@
         <v>4</v>
       </c>
       <c r="Z159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA159">
         <v>4</v>
@@ -15415,7 +15415,7 @@
         <v>4</v>
       </c>
       <c r="F160">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G160">
         <v>4</v>
@@ -15430,22 +15430,22 @@
         <v>4</v>
       </c>
       <c r="K160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L160">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M160">
         <v>4</v>
       </c>
       <c r="N160">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O160">
         <v>3</v>
       </c>
       <c r="P160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q160">
         <v>6</v>
@@ -15454,13 +15454,13 @@
         <v>4</v>
       </c>
       <c r="S160">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T160">
         <v>5</v>
       </c>
       <c r="U160">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V160">
         <v>5</v>
@@ -15469,7 +15469,7 @@
         <v>6</v>
       </c>
       <c r="X160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y160">
         <v>4</v>
@@ -15501,7 +15501,7 @@
         <v>5</v>
       </c>
       <c r="F161">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G161">
         <v>4</v>
@@ -15510,13 +15510,13 @@
         <v>5</v>
       </c>
       <c r="I161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J161">
         <v>5</v>
       </c>
       <c r="K161">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L161">
         <v>4</v>
@@ -15528,7 +15528,7 @@
         <v>3</v>
       </c>
       <c r="O161">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P161">
         <v>5</v>
@@ -15537,13 +15537,13 @@
         <v>6</v>
       </c>
       <c r="R161">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S161">
         <v>6</v>
       </c>
       <c r="T161">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U161">
         <v>6</v>
@@ -15584,7 +15584,7 @@
         <v>270</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F162">
         <v>5</v>
@@ -15596,13 +15596,13 @@
         <v>5</v>
       </c>
       <c r="I162">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J162">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L162">
         <v>6</v>
@@ -15614,13 +15614,13 @@
         <v>3</v>
       </c>
       <c r="O162">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P162">
         <v>5</v>
       </c>
       <c r="Q162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R162">
         <v>7</v>
@@ -15629,13 +15629,13 @@
         <v>5</v>
       </c>
       <c r="T162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U162">
         <v>6</v>
       </c>
       <c r="V162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W162">
         <v>6</v>
@@ -15673,7 +15673,7 @@
         <v>5</v>
       </c>
       <c r="F163">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G163">
         <v>5</v>
@@ -15685,7 +15685,7 @@
         <v>3</v>
       </c>
       <c r="J163">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K163">
         <v>5</v>
@@ -15851,7 +15851,7 @@
         <v>5</v>
       </c>
       <c r="H165">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I165">
         <v>3</v>
@@ -15863,7 +15863,7 @@
         <v>6</v>
       </c>
       <c r="L165">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M165">
         <v>5</v>
@@ -15899,7 +15899,7 @@
         <v>6</v>
       </c>
       <c r="X165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y165">
         <v>1</v>
@@ -15967,25 +15967,25 @@
         <v>6</v>
       </c>
       <c r="R166">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S166">
         <v>6</v>
       </c>
       <c r="T166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U166">
         <v>4</v>
       </c>
       <c r="V166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W166">
         <v>6</v>
       </c>
       <c r="X166">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y166">
         <v>3</v>
@@ -16032,7 +16032,7 @@
         <v>4</v>
       </c>
       <c r="K167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L167">
         <v>4</v>
@@ -16041,13 +16041,13 @@
         <v>4</v>
       </c>
       <c r="N167">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O167">
         <v>4</v>
       </c>
       <c r="P167">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q167">
         <v>6</v>
@@ -16056,13 +16056,13 @@
         <v>5</v>
       </c>
       <c r="S167">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T167">
         <v>5</v>
       </c>
       <c r="U167">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V167">
         <v>4</v>
@@ -16077,10 +16077,10 @@
         <v>4</v>
       </c>
       <c r="Z167">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA167">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB167">
         <v>4</v>
@@ -16103,13 +16103,13 @@
         <v>3</v>
       </c>
       <c r="F168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G168">
         <v>3</v>
       </c>
       <c r="H168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I168">
         <v>5</v>
@@ -16118,7 +16118,7 @@
         <v>4</v>
       </c>
       <c r="K168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L168">
         <v>3</v>
@@ -16139,37 +16139,37 @@
         <v>4</v>
       </c>
       <c r="R168">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S168">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T168">
         <v>5</v>
       </c>
       <c r="U168">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V168">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W168">
         <v>6</v>
       </c>
       <c r="X168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z168">
         <v>2</v>
       </c>
       <c r="AA168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB168">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:28">
@@ -16287,7 +16287,7 @@
         <v>4</v>
       </c>
       <c r="J170">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K170">
         <v>5</v>
@@ -16358,7 +16358,7 @@
         <v>279</v>
       </c>
       <c r="E171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F171">
         <v>3</v>
@@ -16403,13 +16403,13 @@
         <v>4</v>
       </c>
       <c r="T171">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U171">
         <v>5</v>
       </c>
       <c r="V171">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W171">
         <v>6</v>
@@ -16427,7 +16427,7 @@
         <v>1</v>
       </c>
       <c r="AB171">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:28">
@@ -16533,7 +16533,7 @@
         <v>4</v>
       </c>
       <c r="F173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G173">
         <v>5</v>
@@ -16572,16 +16572,16 @@
         <v>6</v>
       </c>
       <c r="S173">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T173">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U173">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V173">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W173">
         <v>6</v>
@@ -16658,7 +16658,7 @@
         <v>5</v>
       </c>
       <c r="S174">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T174">
         <v>7</v>
@@ -16765,7 +16765,7 @@
         <v>2</v>
       </c>
       <c r="Z175">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA175">
         <v>2</v>
@@ -16788,10 +16788,10 @@
         <v>284</v>
       </c>
       <c r="E176">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F176">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G176">
         <v>4</v>
@@ -16800,10 +16800,10 @@
         <v>6</v>
       </c>
       <c r="I176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J176">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K176">
         <v>5</v>
@@ -16812,31 +16812,31 @@
         <v>5</v>
       </c>
       <c r="M176">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N176">
         <v>3</v>
       </c>
       <c r="O176">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P176">
         <v>5</v>
       </c>
       <c r="Q176">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R176">
         <v>4</v>
       </c>
       <c r="S176">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T176">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U176">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V176">
         <v>4</v>
@@ -16845,13 +16845,13 @@
         <v>6</v>
       </c>
       <c r="X176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y176">
         <v>1</v>
       </c>
       <c r="Z176">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA176">
         <v>1</v>
@@ -16883,7 +16883,7 @@
         <v>4</v>
       </c>
       <c r="H177">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I177">
         <v>4</v>
@@ -16966,7 +16966,7 @@
         <v>4</v>
       </c>
       <c r="G178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H178">
         <v>4</v>
@@ -16975,25 +16975,25 @@
         <v>4</v>
       </c>
       <c r="J178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K178">
         <v>5</v>
       </c>
       <c r="L178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M178">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N178">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O178">
         <v>4</v>
       </c>
       <c r="P178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q178">
         <v>5</v>
@@ -17064,7 +17064,7 @@
         <v>4</v>
       </c>
       <c r="K179">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L179">
         <v>5</v>
@@ -17082,37 +17082,37 @@
         <v>4</v>
       </c>
       <c r="Q179">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R179">
         <v>4</v>
       </c>
       <c r="S179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V179">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W179">
         <v>6</v>
       </c>
       <c r="X179">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y179">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z179">
         <v>4</v>
       </c>
       <c r="AA179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB179">
         <v>5</v>
@@ -17159,13 +17159,13 @@
         <v>5</v>
       </c>
       <c r="N180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O180">
         <v>6</v>
       </c>
       <c r="P180">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q180">
         <v>4</v>
@@ -17218,10 +17218,10 @@
         <v>289</v>
       </c>
       <c r="E181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G181">
         <v>4</v>
@@ -17239,7 +17239,7 @@
         <v>5</v>
       </c>
       <c r="L181">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M181">
         <v>5</v>
@@ -17263,10 +17263,10 @@
         <v>3</v>
       </c>
       <c r="T181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V181">
         <v>2</v>
@@ -17275,19 +17275,19 @@
         <v>6</v>
       </c>
       <c r="X181">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y181">
         <v>5</v>
       </c>
       <c r="Z181">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA181">
         <v>5</v>
       </c>
       <c r="AB181">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182" spans="1:28">
@@ -17355,7 +17355,7 @@
         <v>5</v>
       </c>
       <c r="V182">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W182">
         <v>6</v>
@@ -17426,10 +17426,10 @@
         <v>4</v>
       </c>
       <c r="Q183">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R183">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S183">
         <v>3</v>
@@ -17453,7 +17453,7 @@
         <v>4</v>
       </c>
       <c r="Z183">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA183">
         <v>3</v>
@@ -17524,10 +17524,10 @@
         <v>7</v>
       </c>
       <c r="U184">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W184">
         <v>6</v>
@@ -17598,7 +17598,7 @@
         <v>5</v>
       </c>
       <c r="Q185">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R185">
         <v>6</v>
@@ -17696,7 +17696,7 @@
         <v>5</v>
       </c>
       <c r="U186">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V186">
         <v>5</v>
@@ -17820,7 +17820,7 @@
         <v>296</v>
       </c>
       <c r="E188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F188">
         <v>5</v>
@@ -17880,7 +17880,7 @@
         <v>4</v>
       </c>
       <c r="Y188">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z188">
         <v>4</v>
@@ -17889,7 +17889,7 @@
         <v>4</v>
       </c>
       <c r="AB188">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:28">
@@ -17912,7 +17912,7 @@
         <v>5</v>
       </c>
       <c r="G189">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H189">
         <v>5</v>
@@ -17957,7 +17957,7 @@
         <v>5</v>
       </c>
       <c r="V189">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W189">
         <v>6</v>
@@ -17966,7 +17966,7 @@
         <v>3</v>
       </c>
       <c r="Y189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z189">
         <v>1</v>
@@ -17975,7 +17975,7 @@
         <v>2</v>
       </c>
       <c r="AB189">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:28">
@@ -17998,7 +17998,7 @@
         <v>2</v>
       </c>
       <c r="G190">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H190">
         <v>3</v>
@@ -18034,13 +18034,13 @@
         <v>5</v>
       </c>
       <c r="S190">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T190">
         <v>4</v>
       </c>
       <c r="U190">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V190">
         <v>5</v>
@@ -18144,10 +18144,10 @@
         <v>3</v>
       </c>
       <c r="AA191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB191">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:28">
@@ -18164,7 +18164,7 @@
         <v>300</v>
       </c>
       <c r="E192">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F192">
         <v>5</v>
@@ -18176,13 +18176,13 @@
         <v>5</v>
       </c>
       <c r="I192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J192">
         <v>6</v>
       </c>
       <c r="K192">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L192">
         <v>5</v>
@@ -18194,13 +18194,13 @@
         <v>3</v>
       </c>
       <c r="O192">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P192">
         <v>5</v>
       </c>
       <c r="Q192">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R192">
         <v>5</v>
@@ -18221,16 +18221,16 @@
         <v>6</v>
       </c>
       <c r="X192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB192">
         <v>2</v>
@@ -18256,13 +18256,13 @@
         <v>3</v>
       </c>
       <c r="G193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H193">
         <v>2</v>
       </c>
       <c r="I193">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J193">
         <v>2</v>
@@ -18280,43 +18280,43 @@
         <v>5</v>
       </c>
       <c r="O193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P193">
         <v>3</v>
       </c>
       <c r="Q193">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S193">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T193">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V193">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W193">
         <v>6</v>
       </c>
       <c r="X193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA193">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB193">
         <v>6</v>
@@ -18345,7 +18345,7 @@
         <v>5</v>
       </c>
       <c r="H194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I194">
         <v>3</v>
@@ -18363,13 +18363,13 @@
         <v>5</v>
       </c>
       <c r="N194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O194">
         <v>5</v>
       </c>
       <c r="P194">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q194">
         <v>5</v>
@@ -18520,7 +18520,7 @@
         <v>5</v>
       </c>
       <c r="I196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J196">
         <v>4</v>
@@ -18538,7 +18538,7 @@
         <v>4</v>
       </c>
       <c r="O196">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P196">
         <v>4</v>
@@ -18550,7 +18550,7 @@
         <v>3</v>
       </c>
       <c r="S196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T196">
         <v>3</v>
@@ -18565,7 +18565,7 @@
         <v>6</v>
       </c>
       <c r="X196">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y196">
         <v>2</v>
@@ -18577,7 +18577,7 @@
         <v>3</v>
       </c>
       <c r="AB196">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:28">
@@ -18606,13 +18606,13 @@
         <v>4</v>
       </c>
       <c r="I197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J197">
         <v>4</v>
       </c>
       <c r="K197">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L197">
         <v>3</v>
@@ -18624,40 +18624,40 @@
         <v>6</v>
       </c>
       <c r="O197">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P197">
         <v>2</v>
       </c>
       <c r="Q197">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R197">
         <v>5</v>
       </c>
       <c r="S197">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T197">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U197">
         <v>3</v>
       </c>
       <c r="V197">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W197">
         <v>6</v>
       </c>
       <c r="X197">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y197">
         <v>4</v>
       </c>
       <c r="Z197">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA197">
         <v>4</v>
@@ -18778,10 +18778,10 @@
         <v>5</v>
       </c>
       <c r="I199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J199">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K199">
         <v>4</v>
@@ -18796,7 +18796,7 @@
         <v>4</v>
       </c>
       <c r="O199">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P199">
         <v>4</v>
@@ -18829,13 +18829,13 @@
         <v>3</v>
       </c>
       <c r="Z199">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA199">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB199">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:28">
@@ -18873,7 +18873,7 @@
         <v>5</v>
       </c>
       <c r="L200">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M200">
         <v>4</v>
@@ -18888,13 +18888,13 @@
         <v>4</v>
       </c>
       <c r="Q200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R200">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S200">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T200">
         <v>4</v>
@@ -18921,7 +18921,7 @@
         <v>3</v>
       </c>
       <c r="AB200">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:28">
@@ -19027,7 +19027,7 @@
         <v>5</v>
       </c>
       <c r="F202">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G202">
         <v>6</v>
@@ -19045,10 +19045,10 @@
         <v>5</v>
       </c>
       <c r="L202">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M202">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N202">
         <v>4</v>
@@ -19060,7 +19060,7 @@
         <v>4</v>
       </c>
       <c r="Q202">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R202">
         <v>5</v>
@@ -19090,10 +19090,10 @@
         <v>1</v>
       </c>
       <c r="AA202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB202">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:28">
@@ -19113,7 +19113,7 @@
         <v>6</v>
       </c>
       <c r="F203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G203">
         <v>6</v>
@@ -19137,25 +19137,25 @@
         <v>5</v>
       </c>
       <c r="N203">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O203">
         <v>5</v>
       </c>
       <c r="P203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q203">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R203">
         <v>5</v>
       </c>
       <c r="S203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T203">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U203">
         <v>6</v>
@@ -19170,7 +19170,7 @@
         <v>2</v>
       </c>
       <c r="Y203">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z203">
         <v>2</v>
@@ -19262,7 +19262,7 @@
         <v>1</v>
       </c>
       <c r="AA204">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB204">
         <v>3</v>
@@ -19288,7 +19288,7 @@
         <v>5</v>
       </c>
       <c r="G205">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H205">
         <v>4</v>
@@ -19511,7 +19511,7 @@
         <v>6</v>
       </c>
       <c r="X207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y207">
         <v>3</v>
@@ -19520,7 +19520,7 @@
         <v>3</v>
       </c>
       <c r="AA207">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB207">
         <v>3</v>
@@ -19540,10 +19540,10 @@
         <v>316</v>
       </c>
       <c r="E208">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F208">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G208">
         <v>4</v>
@@ -19567,13 +19567,13 @@
         <v>3</v>
       </c>
       <c r="N208">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O208">
         <v>3</v>
       </c>
       <c r="P208">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q208">
         <v>4</v>
@@ -19585,31 +19585,31 @@
         <v>3</v>
       </c>
       <c r="T208">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U208">
         <v>4</v>
       </c>
       <c r="V208">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W208">
         <v>6</v>
       </c>
       <c r="X208">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y208">
         <v>3</v>
       </c>
       <c r="Z208">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA208">
         <v>4</v>
       </c>
       <c r="AB208">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:28">
@@ -19626,10 +19626,10 @@
         <v>317</v>
       </c>
       <c r="E209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F209">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G209">
         <v>2</v>
@@ -19638,7 +19638,7 @@
         <v>4</v>
       </c>
       <c r="I209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J209">
         <v>4</v>
@@ -19650,13 +19650,13 @@
         <v>4</v>
       </c>
       <c r="M209">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N209">
         <v>5</v>
       </c>
       <c r="O209">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P209">
         <v>3</v>
@@ -19668,16 +19668,16 @@
         <v>3</v>
       </c>
       <c r="S209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U209">
         <v>2</v>
       </c>
       <c r="V209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W209">
         <v>6</v>
@@ -19692,7 +19692,7 @@
         <v>6</v>
       </c>
       <c r="AA209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB209">
         <v>6</v>
@@ -19712,7 +19712,7 @@
         <v>318</v>
       </c>
       <c r="E210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F210">
         <v>5</v>
@@ -19727,16 +19727,16 @@
         <v>4</v>
       </c>
       <c r="J210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K210">
         <v>4</v>
       </c>
       <c r="L210">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M210">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N210">
         <v>3</v>
@@ -19751,34 +19751,34 @@
         <v>3</v>
       </c>
       <c r="R210">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S210">
         <v>4</v>
       </c>
       <c r="T210">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U210">
         <v>4</v>
       </c>
       <c r="V210">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W210">
         <v>6</v>
       </c>
       <c r="X210">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z210">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB210">
         <v>3</v>
@@ -19846,7 +19846,7 @@
         <v>5</v>
       </c>
       <c r="U211">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V211">
         <v>5</v>
@@ -20006,7 +20006,7 @@
         <v>3</v>
       </c>
       <c r="Q213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R213">
         <v>3</v>
@@ -20030,7 +20030,7 @@
         <v>5</v>
       </c>
       <c r="Y213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z213">
         <v>5</v>
@@ -20231,7 +20231,7 @@
         <v>3</v>
       </c>
       <c r="F216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G216">
         <v>4</v>
@@ -20240,10 +20240,10 @@
         <v>3</v>
       </c>
       <c r="I216">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K216">
         <v>4</v>
@@ -20258,7 +20258,7 @@
         <v>4</v>
       </c>
       <c r="O216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P216">
         <v>4</v>
@@ -20270,10 +20270,10 @@
         <v>4</v>
       </c>
       <c r="S216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U216">
         <v>5</v>
@@ -20285,10 +20285,10 @@
         <v>6</v>
       </c>
       <c r="X216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y216">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z216">
         <v>6</v>
@@ -20329,16 +20329,16 @@
         <v>3</v>
       </c>
       <c r="J217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N217">
         <v>3</v>
@@ -20353,7 +20353,7 @@
         <v>2</v>
       </c>
       <c r="R217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S217">
         <v>4</v>
@@ -20365,7 +20365,7 @@
         <v>3</v>
       </c>
       <c r="V217">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W217">
         <v>6</v>
@@ -20495,7 +20495,7 @@
         <v>5</v>
       </c>
       <c r="H219">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I219">
         <v>3</v>
@@ -20575,19 +20575,19 @@
         <v>4</v>
       </c>
       <c r="F220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G220">
         <v>3</v>
       </c>
       <c r="H220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I220">
         <v>4</v>
       </c>
       <c r="J220">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K220">
         <v>5</v>
@@ -20629,19 +20629,19 @@
         <v>6</v>
       </c>
       <c r="X220">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y220">
         <v>2</v>
       </c>
       <c r="Z220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA220">
         <v>4</v>
       </c>
       <c r="AB220">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:28">
@@ -20866,7 +20866,7 @@
         <v>4</v>
       </c>
       <c r="Q223">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R223">
         <v>3</v>
@@ -21023,19 +21023,19 @@
         <v>4</v>
       </c>
       <c r="L225">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M225">
         <v>4</v>
       </c>
       <c r="N225">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O225">
         <v>5</v>
       </c>
       <c r="P225">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q225">
         <v>5</v>
@@ -21044,7 +21044,7 @@
         <v>5</v>
       </c>
       <c r="S225">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T225">
         <v>5</v>
@@ -21065,10 +21065,10 @@
         <v>4</v>
       </c>
       <c r="Z225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA225">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB225">
         <v>5</v>
@@ -21133,13 +21133,13 @@
         <v>5</v>
       </c>
       <c r="T226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U226">
         <v>4</v>
       </c>
       <c r="V226">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W226">
         <v>6</v>
@@ -21157,7 +21157,7 @@
         <v>3</v>
       </c>
       <c r="AB226">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:28">
@@ -21174,19 +21174,19 @@
         <v>335</v>
       </c>
       <c r="E227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F227">
         <v>4</v>
       </c>
       <c r="G227">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H227">
         <v>5</v>
       </c>
       <c r="I227">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J227">
         <v>5</v>
@@ -21204,16 +21204,16 @@
         <v>2</v>
       </c>
       <c r="O227">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P227">
         <v>6</v>
       </c>
       <c r="Q227">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R227">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S227">
         <v>6</v>
@@ -21225,7 +21225,7 @@
         <v>5</v>
       </c>
       <c r="V227">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W227">
         <v>6</v>
@@ -21234,13 +21234,13 @@
         <v>4</v>
       </c>
       <c r="Y227">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z227">
         <v>4</v>
       </c>
       <c r="AA227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB227">
         <v>4</v>
@@ -21266,13 +21266,13 @@
         <v>4</v>
       </c>
       <c r="G228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H228">
         <v>4</v>
       </c>
       <c r="I228">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J228">
         <v>4</v>
@@ -21290,7 +21290,7 @@
         <v>4</v>
       </c>
       <c r="O228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P228">
         <v>4</v>
@@ -21299,7 +21299,7 @@
         <v>5</v>
       </c>
       <c r="R228">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S228">
         <v>7</v>
@@ -21323,10 +21323,10 @@
         <v>2</v>
       </c>
       <c r="Z228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA228">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB228">
         <v>2</v>
@@ -21361,13 +21361,13 @@
         <v>4</v>
       </c>
       <c r="J229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L229">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M229">
         <v>4</v>
@@ -21382,7 +21382,7 @@
         <v>5</v>
       </c>
       <c r="Q229">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R229">
         <v>3</v>
@@ -21391,19 +21391,19 @@
         <v>4</v>
       </c>
       <c r="T229">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V229">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W229">
         <v>6</v>
       </c>
       <c r="X229">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y229">
         <v>3</v>
@@ -21444,7 +21444,7 @@
         <v>3</v>
       </c>
       <c r="I230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J230">
         <v>3</v>
@@ -21462,7 +21462,7 @@
         <v>5</v>
       </c>
       <c r="O230">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P230">
         <v>3</v>
@@ -21480,19 +21480,19 @@
         <v>2</v>
       </c>
       <c r="U230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W230">
         <v>6</v>
       </c>
       <c r="X230">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z230">
         <v>4</v>
@@ -21530,7 +21530,7 @@
         <v>4</v>
       </c>
       <c r="I231">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J231">
         <v>5</v>
@@ -21545,28 +21545,28 @@
         <v>4</v>
       </c>
       <c r="N231">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q231">
         <v>6</v>
       </c>
       <c r="R231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S231">
         <v>5</v>
       </c>
       <c r="T231">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U231">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V231">
         <v>6</v>
@@ -21575,7 +21575,7 @@
         <v>6</v>
       </c>
       <c r="X231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y231">
         <v>2</v>
@@ -21584,7 +21584,7 @@
         <v>2</v>
       </c>
       <c r="AA231">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB231">
         <v>2</v>
@@ -21622,7 +21622,7 @@
         <v>6</v>
       </c>
       <c r="K232">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L232">
         <v>5</v>
@@ -21643,10 +21643,10 @@
         <v>5</v>
       </c>
       <c r="R232">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S232">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T232">
         <v>4</v>
@@ -21655,7 +21655,7 @@
         <v>4</v>
       </c>
       <c r="V232">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W232">
         <v>6</v>
@@ -21670,7 +21670,7 @@
         <v>4</v>
       </c>
       <c r="AA232">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB232">
         <v>3</v>
@@ -21690,7 +21690,7 @@
         <v>341</v>
       </c>
       <c r="E233">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F233">
         <v>6</v>
@@ -21776,7 +21776,7 @@
         <v>342</v>
       </c>
       <c r="E234">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F234">
         <v>6</v>
@@ -21803,13 +21803,13 @@
         <v>5</v>
       </c>
       <c r="N234">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O234">
         <v>5</v>
       </c>
       <c r="P234">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q234">
         <v>2</v>
@@ -21824,7 +21824,7 @@
         <v>4</v>
       </c>
       <c r="U234">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V234">
         <v>4</v>
@@ -21842,7 +21842,7 @@
         <v>4</v>
       </c>
       <c r="AA234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB234">
         <v>4</v>
@@ -21931,7 +21931,7 @@
         <v>3</v>
       </c>
       <c r="AB235">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:28">
@@ -21987,7 +21987,7 @@
         <v>3</v>
       </c>
       <c r="R236">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S236">
         <v>4</v>
@@ -22046,7 +22046,7 @@
         <v>3</v>
       </c>
       <c r="I237">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J237">
         <v>3</v>
@@ -22064,7 +22064,7 @@
         <v>4</v>
       </c>
       <c r="O237">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P237">
         <v>4</v>
@@ -22097,7 +22097,7 @@
         <v>4</v>
       </c>
       <c r="Z237">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA237">
         <v>2</v>
@@ -22126,7 +22126,7 @@
         <v>4</v>
       </c>
       <c r="G238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H238">
         <v>4</v>
@@ -22135,43 +22135,43 @@
         <v>4</v>
       </c>
       <c r="J238">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K238">
         <v>4</v>
       </c>
       <c r="L238">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N238">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O238">
         <v>4</v>
       </c>
       <c r="P238">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U238">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W238">
         <v>6</v>
@@ -22180,13 +22180,13 @@
         <v>3</v>
       </c>
       <c r="Y238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB238">
         <v>2</v>
@@ -22212,16 +22212,16 @@
         <v>5</v>
       </c>
       <c r="G239">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H239">
         <v>5</v>
       </c>
       <c r="I239">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J239">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K239">
         <v>5</v>
@@ -22236,7 +22236,7 @@
         <v>2</v>
       </c>
       <c r="O239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P239">
         <v>6</v>
@@ -22251,10 +22251,10 @@
         <v>5</v>
       </c>
       <c r="T239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U239">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V239">
         <v>4</v>
@@ -22352,16 +22352,16 @@
         <v>3</v>
       </c>
       <c r="Y240">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z240">
         <v>3</v>
       </c>
       <c r="AA240">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB240">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241" spans="1:28">
@@ -22381,10 +22381,10 @@
         <v>4</v>
       </c>
       <c r="F241">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G241">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H241">
         <v>4</v>
@@ -22405,13 +22405,13 @@
         <v>4</v>
       </c>
       <c r="N241">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O241">
         <v>5</v>
       </c>
       <c r="P241">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q241">
         <v>3</v>
@@ -22423,13 +22423,13 @@
         <v>3</v>
       </c>
       <c r="T241">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U241">
         <v>3</v>
       </c>
       <c r="V241">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W241">
         <v>6</v>
@@ -22441,13 +22441,13 @@
         <v>7</v>
       </c>
       <c r="Z241">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA241">
         <v>5</v>
       </c>
       <c r="AB241">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:28">
@@ -22479,7 +22479,7 @@
         <v>3</v>
       </c>
       <c r="J242">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K242">
         <v>5</v>
@@ -22512,7 +22512,7 @@
         <v>3</v>
       </c>
       <c r="U242">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V242">
         <v>3</v>
@@ -22559,7 +22559,7 @@
         <v>4</v>
       </c>
       <c r="H243">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I243">
         <v>4</v>
@@ -22568,7 +22568,7 @@
         <v>4</v>
       </c>
       <c r="K243">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L243">
         <v>4</v>
@@ -22592,10 +22592,10 @@
         <v>3</v>
       </c>
       <c r="S243">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T243">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U243">
         <v>4</v>
@@ -22610,13 +22610,13 @@
         <v>2</v>
       </c>
       <c r="Y243">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z243">
         <v>2</v>
       </c>
       <c r="AA243">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB243">
         <v>2</v>
@@ -22642,7 +22642,7 @@
         <v>5</v>
       </c>
       <c r="G244">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H244">
         <v>4</v>
@@ -22675,7 +22675,7 @@
         <v>4</v>
       </c>
       <c r="R244">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S244">
         <v>4</v>
@@ -22687,7 +22687,7 @@
         <v>3</v>
       </c>
       <c r="V244">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W244">
         <v>6</v>
@@ -22702,7 +22702,7 @@
         <v>2</v>
       </c>
       <c r="AA244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB244">
         <v>1</v>
@@ -22731,13 +22731,13 @@
         <v>4</v>
       </c>
       <c r="H245">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I245">
         <v>3</v>
       </c>
       <c r="J245">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K245">
         <v>5</v>
@@ -22758,7 +22758,7 @@
         <v>4</v>
       </c>
       <c r="Q245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R245">
         <v>3</v>
@@ -22770,10 +22770,10 @@
         <v>3</v>
       </c>
       <c r="U245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V245">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W245">
         <v>6</v>
@@ -22785,7 +22785,7 @@
         <v>4</v>
       </c>
       <c r="Z245">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA245">
         <v>4</v>
@@ -22808,13 +22808,13 @@
         <v>354</v>
       </c>
       <c r="E246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F246">
         <v>5</v>
       </c>
       <c r="G246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H246">
         <v>5</v>
@@ -22826,7 +22826,7 @@
         <v>4</v>
       </c>
       <c r="K246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L246">
         <v>4</v>
@@ -22844,13 +22844,13 @@
         <v>4</v>
       </c>
       <c r="Q246">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R246">
         <v>4</v>
       </c>
       <c r="S246">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T246">
         <v>5</v>
@@ -22909,7 +22909,7 @@
         <v>3</v>
       </c>
       <c r="J247">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K247">
         <v>5</v>
@@ -23022,7 +23022,7 @@
         <v>4</v>
       </c>
       <c r="S248">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T248">
         <v>4</v>
@@ -23037,7 +23037,7 @@
         <v>6</v>
       </c>
       <c r="X248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y248">
         <v>3</v>
@@ -23046,10 +23046,10 @@
         <v>3</v>
       </c>
       <c r="AA248">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB248">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249" spans="1:28">
@@ -23084,7 +23084,7 @@
         <v>5</v>
       </c>
       <c r="K249">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L249">
         <v>5</v>
@@ -23093,13 +23093,13 @@
         <v>5</v>
       </c>
       <c r="N249">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O249">
         <v>5</v>
       </c>
       <c r="P249">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q249">
         <v>4</v>
@@ -23126,7 +23126,7 @@
         <v>4</v>
       </c>
       <c r="Y249">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z249">
         <v>3</v>
@@ -23191,7 +23191,7 @@
         <v>3</v>
       </c>
       <c r="R250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S250">
         <v>5</v>
@@ -23244,7 +23244,7 @@
         <v>6</v>
       </c>
       <c r="G251">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H251">
         <v>5</v>
@@ -23324,7 +23324,7 @@
         <v>360</v>
       </c>
       <c r="E252">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F252">
         <v>6</v>
@@ -23336,43 +23336,43 @@
         <v>6</v>
       </c>
       <c r="I252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J252">
         <v>5</v>
       </c>
       <c r="K252">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L252">
         <v>5</v>
       </c>
       <c r="M252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N252">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q252">
         <v>7</v>
       </c>
       <c r="R252">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T252">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V252">
         <v>6</v>
@@ -23381,13 +23381,13 @@
         <v>6</v>
       </c>
       <c r="X252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y252">
         <v>1</v>
       </c>
       <c r="Z252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA252">
         <v>3</v>
@@ -23499,7 +23499,7 @@
         <v>6</v>
       </c>
       <c r="F254">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G254">
         <v>6</v>
@@ -23508,7 +23508,7 @@
         <v>6</v>
       </c>
       <c r="I254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J254">
         <v>5</v>
@@ -23523,13 +23523,13 @@
         <v>6</v>
       </c>
       <c r="N254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O254">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P254">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q254">
         <v>6</v>
@@ -23594,7 +23594,7 @@
         <v>4</v>
       </c>
       <c r="I255">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J255">
         <v>3</v>
@@ -23612,13 +23612,13 @@
         <v>5</v>
       </c>
       <c r="O255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P255">
         <v>3</v>
       </c>
       <c r="Q255">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R255">
         <v>4</v>
@@ -23630,7 +23630,7 @@
         <v>2</v>
       </c>
       <c r="U255">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V255">
         <v>3</v>
@@ -23639,16 +23639,16 @@
         <v>6</v>
       </c>
       <c r="X255">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y255">
         <v>4</v>
       </c>
       <c r="Z255">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA255">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB255">
         <v>4</v>
@@ -23704,7 +23704,7 @@
         <v>4</v>
       </c>
       <c r="Q256">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R256">
         <v>5</v>
@@ -23713,13 +23713,13 @@
         <v>3</v>
       </c>
       <c r="T256">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U256">
         <v>4</v>
       </c>
       <c r="V256">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W256">
         <v>6</v>
@@ -23728,10 +23728,10 @@
         <v>4</v>
       </c>
       <c r="Y256">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z256">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA256">
         <v>5</v>
@@ -23781,13 +23781,13 @@
         <v>4</v>
       </c>
       <c r="N257">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O257">
         <v>4</v>
       </c>
       <c r="P257">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q257">
         <v>3</v>
@@ -23796,7 +23796,7 @@
         <v>4</v>
       </c>
       <c r="S257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T257">
         <v>5</v>
@@ -23888,7 +23888,7 @@
         <v>5</v>
       </c>
       <c r="U258">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V258">
         <v>6</v>
@@ -24015,7 +24015,7 @@
         <v>4</v>
       </c>
       <c r="F260">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G260">
         <v>4</v>
@@ -24039,13 +24039,13 @@
         <v>5</v>
       </c>
       <c r="N260">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O260">
         <v>3</v>
       </c>
       <c r="P260">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q260">
         <v>5</v>
@@ -24078,7 +24078,7 @@
         <v>2</v>
       </c>
       <c r="AA260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB260">
         <v>1</v>
@@ -24101,7 +24101,7 @@
         <v>5</v>
       </c>
       <c r="F261">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G261">
         <v>5</v>
@@ -24119,10 +24119,10 @@
         <v>5</v>
       </c>
       <c r="L261">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M261">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N261">
         <v>4</v>
@@ -24190,13 +24190,13 @@
         <v>3</v>
       </c>
       <c r="G262">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H262">
         <v>4</v>
       </c>
       <c r="I262">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J262">
         <v>5</v>
@@ -24214,7 +24214,7 @@
         <v>4</v>
       </c>
       <c r="O262">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P262">
         <v>4</v>
@@ -24244,7 +24244,7 @@
         <v>2</v>
       </c>
       <c r="Y262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z262">
         <v>3</v>
@@ -24330,7 +24330,7 @@
         <v>3</v>
       </c>
       <c r="Y263">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z263">
         <v>4</v>
@@ -24356,13 +24356,13 @@
         <v>372</v>
       </c>
       <c r="E264">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F264">
         <v>3</v>
       </c>
       <c r="G264">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H264">
         <v>4</v>
@@ -24377,10 +24377,10 @@
         <v>3</v>
       </c>
       <c r="L264">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M264">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N264">
         <v>3</v>
@@ -24395,7 +24395,7 @@
         <v>5</v>
       </c>
       <c r="R264">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S264">
         <v>5</v>
@@ -24407,16 +24407,16 @@
         <v>5</v>
       </c>
       <c r="V264">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W264">
         <v>6</v>
       </c>
       <c r="X264">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y264">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z264">
         <v>2</v>
@@ -24442,13 +24442,13 @@
         <v>373</v>
       </c>
       <c r="E265">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F265">
         <v>5</v>
       </c>
       <c r="G265">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H265">
         <v>5</v>
@@ -24469,22 +24469,22 @@
         <v>5</v>
       </c>
       <c r="N265">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O265">
         <v>4</v>
       </c>
       <c r="P265">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q265">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R265">
         <v>6</v>
       </c>
       <c r="S265">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T265">
         <v>6</v>
@@ -24502,10 +24502,10 @@
         <v>3</v>
       </c>
       <c r="Y265">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z265">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA265">
         <v>2</v>
@@ -24635,7 +24635,7 @@
         <v>6</v>
       </c>
       <c r="L267">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M267">
         <v>5</v>
@@ -24914,7 +24914,7 @@
         <v>4</v>
       </c>
       <c r="S270">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T270">
         <v>4</v>
@@ -24932,7 +24932,7 @@
         <v>2</v>
       </c>
       <c r="Y270">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z270">
         <v>4</v>
@@ -24958,7 +24958,7 @@
         <v>379</v>
       </c>
       <c r="E271">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F271">
         <v>5</v>
@@ -24967,7 +24967,7 @@
         <v>5</v>
       </c>
       <c r="H271">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I271">
         <v>3</v>
@@ -24982,7 +24982,7 @@
         <v>5</v>
       </c>
       <c r="M271">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N271">
         <v>3</v>
@@ -24994,13 +24994,13 @@
         <v>5</v>
       </c>
       <c r="Q271">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R271">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S271">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T271">
         <v>6</v>
@@ -25015,7 +25015,7 @@
         <v>6</v>
       </c>
       <c r="X271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y271">
         <v>3</v>
@@ -25027,7 +25027,7 @@
         <v>4</v>
       </c>
       <c r="AB271">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="272" spans="1:28">
@@ -25044,13 +25044,13 @@
         <v>380</v>
       </c>
       <c r="E272">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F272">
         <v>4</v>
       </c>
       <c r="G272">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H272">
         <v>4</v>
@@ -25059,7 +25059,7 @@
         <v>3</v>
       </c>
       <c r="J272">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K272">
         <v>5</v>
@@ -25068,7 +25068,7 @@
         <v>5</v>
       </c>
       <c r="M272">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N272">
         <v>4</v>
@@ -25095,7 +25095,7 @@
         <v>4</v>
       </c>
       <c r="V272">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W272">
         <v>6</v>
@@ -25133,7 +25133,7 @@
         <v>3</v>
       </c>
       <c r="F273">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G273">
         <v>4</v>
@@ -25145,7 +25145,7 @@
         <v>4</v>
       </c>
       <c r="J273">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K273">
         <v>3</v>
@@ -25169,7 +25169,7 @@
         <v>4</v>
       </c>
       <c r="R273">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S273">
         <v>6</v>
@@ -25181,16 +25181,16 @@
         <v>5</v>
       </c>
       <c r="V273">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W273">
         <v>6</v>
       </c>
       <c r="X273">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z273">
         <v>2</v>
@@ -25199,7 +25199,7 @@
         <v>3</v>
       </c>
       <c r="AB273">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:28">
@@ -25240,7 +25240,7 @@
         <v>6</v>
       </c>
       <c r="M274">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N274">
         <v>4</v>
@@ -25305,7 +25305,7 @@
         <v>6</v>
       </c>
       <c r="F275">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G275">
         <v>6</v>
@@ -25317,7 +25317,7 @@
         <v>2</v>
       </c>
       <c r="J275">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K275">
         <v>5</v>
@@ -25338,19 +25338,19 @@
         <v>5</v>
       </c>
       <c r="Q275">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R275">
         <v>6</v>
       </c>
       <c r="S275">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T275">
         <v>6</v>
       </c>
       <c r="U275">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V275">
         <v>5</v>
@@ -25365,13 +25365,13 @@
         <v>2</v>
       </c>
       <c r="Z275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB275">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276" spans="1:28">
@@ -25388,25 +25388,25 @@
         <v>384</v>
       </c>
       <c r="E276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F276">
         <v>2</v>
       </c>
       <c r="G276">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H276">
         <v>3</v>
       </c>
       <c r="I276">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J276">
         <v>2</v>
       </c>
       <c r="K276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L276">
         <v>4</v>
@@ -25418,7 +25418,7 @@
         <v>5</v>
       </c>
       <c r="O276">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P276">
         <v>3</v>
@@ -25430,7 +25430,7 @@
         <v>4</v>
       </c>
       <c r="S276">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T276">
         <v>4</v>
@@ -25448,16 +25448,16 @@
         <v>3</v>
       </c>
       <c r="Y276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA276">
         <v>3</v>
       </c>
       <c r="AB276">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277" spans="1:28">
@@ -25489,7 +25489,7 @@
         <v>4</v>
       </c>
       <c r="J277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K277">
         <v>4</v>
@@ -25543,7 +25543,7 @@
         <v>2</v>
       </c>
       <c r="AB277">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278" spans="1:28">
@@ -25572,7 +25572,7 @@
         <v>5</v>
       </c>
       <c r="I278">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J278">
         <v>4</v>
@@ -25590,7 +25590,7 @@
         <v>4</v>
       </c>
       <c r="O278">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P278">
         <v>4</v>
@@ -25599,7 +25599,7 @@
         <v>6</v>
       </c>
       <c r="R278">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S278">
         <v>7</v>
@@ -25611,7 +25611,7 @@
         <v>6</v>
       </c>
       <c r="V278">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W278">
         <v>6</v>
@@ -25688,7 +25688,7 @@
         <v>6</v>
       </c>
       <c r="S279">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T279">
         <v>4</v>
@@ -25706,7 +25706,7 @@
         <v>1</v>
       </c>
       <c r="Y279">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z279">
         <v>1</v>
@@ -25738,7 +25738,7 @@
         <v>5</v>
       </c>
       <c r="G280">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H280">
         <v>5</v>
@@ -25750,13 +25750,13 @@
         <v>5</v>
       </c>
       <c r="K280">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L280">
         <v>4</v>
       </c>
       <c r="M280">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N280">
         <v>4</v>
@@ -25768,19 +25768,19 @@
         <v>4</v>
       </c>
       <c r="Q280">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R280">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S280">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T280">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U280">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V280">
         <v>6</v>
@@ -25789,19 +25789,19 @@
         <v>6</v>
       </c>
       <c r="X280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z280">
         <v>2</v>
       </c>
       <c r="AA280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB280">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281" spans="1:28">
@@ -25904,19 +25904,19 @@
         <v>390</v>
       </c>
       <c r="E282">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F282">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G282">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H282">
         <v>6</v>
       </c>
       <c r="I282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J282">
         <v>6</v>
@@ -25931,13 +25931,13 @@
         <v>6</v>
       </c>
       <c r="N282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O282">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P282">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q282">
         <v>7</v>
@@ -25961,7 +25961,7 @@
         <v>6</v>
       </c>
       <c r="X282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y282">
         <v>1</v>
@@ -25970,10 +25970,10 @@
         <v>1</v>
       </c>
       <c r="AA282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB282">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283" spans="1:28">
@@ -25999,7 +25999,7 @@
         <v>4</v>
       </c>
       <c r="H283">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I283">
         <v>5</v>
@@ -26026,7 +26026,7 @@
         <v>2</v>
       </c>
       <c r="Q283">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R283">
         <v>5</v>
@@ -26056,7 +26056,7 @@
         <v>4</v>
       </c>
       <c r="AA283">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB283">
         <v>4</v>
@@ -26082,7 +26082,7 @@
         <v>5</v>
       </c>
       <c r="G284">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H284">
         <v>4</v>
@@ -26115,10 +26115,10 @@
         <v>5</v>
       </c>
       <c r="R284">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S284">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T284">
         <v>4</v>
@@ -26145,7 +26145,7 @@
         <v>4</v>
       </c>
       <c r="AB284">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285" spans="1:28">
@@ -26180,7 +26180,7 @@
         <v>5</v>
       </c>
       <c r="K285">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L285">
         <v>6</v>
@@ -26397,7 +26397,7 @@
         <v>6</v>
       </c>
       <c r="Z287">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA287">
         <v>4</v>
@@ -26420,7 +26420,7 @@
         <v>396</v>
       </c>
       <c r="E288">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F288">
         <v>4</v>
@@ -26515,7 +26515,7 @@
         <v>5</v>
       </c>
       <c r="H289">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I289">
         <v>3</v>
@@ -26551,7 +26551,7 @@
         <v>4</v>
       </c>
       <c r="T289">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U289">
         <v>4</v>
@@ -26566,16 +26566,16 @@
         <v>1</v>
       </c>
       <c r="Y289">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z289">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA289">
         <v>2</v>
       </c>
       <c r="AB289">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="290" spans="1:28">
@@ -26592,7 +26592,7 @@
         <v>398</v>
       </c>
       <c r="E290">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F290">
         <v>5</v>
@@ -26628,22 +26628,22 @@
         <v>4</v>
       </c>
       <c r="Q290">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R290">
         <v>7</v>
       </c>
       <c r="S290">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T290">
         <v>7</v>
       </c>
       <c r="U290">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V290">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W290">
         <v>6</v>
@@ -26678,10 +26678,10 @@
         <v>399</v>
       </c>
       <c r="E291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G291">
         <v>4</v>
@@ -26693,7 +26693,7 @@
         <v>4</v>
       </c>
       <c r="J291">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K291">
         <v>4</v>
@@ -26791,13 +26791,13 @@
         <v>6</v>
       </c>
       <c r="N292">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O292">
         <v>5</v>
       </c>
       <c r="P292">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q292">
         <v>5</v>
@@ -26862,13 +26862,13 @@
         <v>4</v>
       </c>
       <c r="I293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J293">
         <v>3</v>
       </c>
       <c r="K293">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L293">
         <v>4</v>
@@ -26880,28 +26880,28 @@
         <v>4</v>
       </c>
       <c r="O293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P293">
         <v>4</v>
       </c>
       <c r="Q293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R293">
         <v>3</v>
       </c>
       <c r="S293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U293">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W293">
         <v>6</v>
@@ -26910,7 +26910,7 @@
         <v>4</v>
       </c>
       <c r="Y293">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z293">
         <v>2</v>
@@ -26919,7 +26919,7 @@
         <v>3</v>
       </c>
       <c r="AB293">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:28">
@@ -26942,7 +26942,7 @@
         <v>5</v>
       </c>
       <c r="G294">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H294">
         <v>4</v>
@@ -26957,7 +26957,7 @@
         <v>3</v>
       </c>
       <c r="L294">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M294">
         <v>4</v>
@@ -26972,19 +26972,19 @@
         <v>5</v>
       </c>
       <c r="Q294">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R294">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S294">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T294">
         <v>3</v>
       </c>
       <c r="U294">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V294">
         <v>2</v>
@@ -26996,10 +26996,10 @@
         <v>6</v>
       </c>
       <c r="Y294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z294">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA294">
         <v>3</v>
@@ -27135,13 +27135,13 @@
         <v>6</v>
       </c>
       <c r="N296">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O296">
         <v>6</v>
       </c>
       <c r="P296">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q296">
         <v>6</v>
@@ -27221,13 +27221,13 @@
         <v>5</v>
       </c>
       <c r="N297">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O297">
         <v>5</v>
       </c>
       <c r="P297">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q297">
         <v>5</v>
@@ -27372,7 +27372,7 @@
         <v>3</v>
       </c>
       <c r="G299">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H299">
         <v>3</v>
@@ -27384,7 +27384,7 @@
         <v>3</v>
       </c>
       <c r="K299">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L299">
         <v>3</v>
@@ -27408,7 +27408,7 @@
         <v>3</v>
       </c>
       <c r="S299">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T299">
         <v>5</v>
@@ -27423,7 +27423,7 @@
         <v>6</v>
       </c>
       <c r="X299">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y299">
         <v>2</v>
@@ -27435,7 +27435,7 @@
         <v>3</v>
       </c>
       <c r="AB299">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300" spans="1:28">
@@ -27455,13 +27455,13 @@
         <v>3</v>
       </c>
       <c r="F300">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G300">
         <v>4</v>
       </c>
       <c r="H300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I300">
         <v>5</v>
@@ -27488,10 +27488,10 @@
         <v>4</v>
       </c>
       <c r="Q300">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R300">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S300">
         <v>7</v>
@@ -27500,16 +27500,16 @@
         <v>7</v>
       </c>
       <c r="U300">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V300">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W300">
         <v>6</v>
       </c>
       <c r="X300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y300">
         <v>2</v>
@@ -27518,7 +27518,7 @@
         <v>2</v>
       </c>
       <c r="AA300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB300">
         <v>2</v>
@@ -27574,7 +27574,7 @@
         <v>5</v>
       </c>
       <c r="Q301">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R301">
         <v>5</v>
@@ -27630,7 +27630,7 @@
         <v>5</v>
       </c>
       <c r="G302">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H302">
         <v>6</v>
@@ -27841,7 +27841,7 @@
         <v>4</v>
       </c>
       <c r="T304">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U304">
         <v>5</v>
@@ -27862,7 +27862,7 @@
         <v>2</v>
       </c>
       <c r="AA304">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB304">
         <v>2</v>
@@ -27906,7 +27906,7 @@
         <v>6</v>
       </c>
       <c r="M305">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N305">
         <v>3</v>
@@ -27930,7 +27930,7 @@
         <v>5</v>
       </c>
       <c r="U305">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V305">
         <v>6</v>
@@ -27971,7 +27971,7 @@
         <v>5</v>
       </c>
       <c r="F306">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G306">
         <v>5</v>
@@ -27980,7 +27980,7 @@
         <v>4</v>
       </c>
       <c r="I306">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J306">
         <v>5</v>
@@ -27998,7 +27998,7 @@
         <v>3</v>
       </c>
       <c r="O306">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P306">
         <v>5</v>
@@ -28013,7 +28013,7 @@
         <v>6</v>
       </c>
       <c r="T306">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U306">
         <v>6</v>
@@ -28057,7 +28057,7 @@
         <v>4</v>
       </c>
       <c r="F307">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G307">
         <v>5</v>
@@ -28066,13 +28066,13 @@
         <v>5</v>
       </c>
       <c r="I307">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J307">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K307">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L307">
         <v>5</v>
@@ -28084,7 +28084,7 @@
         <v>2</v>
       </c>
       <c r="O307">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P307">
         <v>6</v>
@@ -28093,7 +28093,7 @@
         <v>6</v>
       </c>
       <c r="R307">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S307">
         <v>6</v>
@@ -28143,7 +28143,7 @@
         <v>5</v>
       </c>
       <c r="F308">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G308">
         <v>6</v>
@@ -28164,7 +28164,7 @@
         <v>5</v>
       </c>
       <c r="M308">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N308">
         <v>3</v>
@@ -28176,7 +28176,7 @@
         <v>5</v>
       </c>
       <c r="Q308">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R308">
         <v>6</v>
@@ -28265,7 +28265,7 @@
         <v>4</v>
       </c>
       <c r="R309">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S309">
         <v>5</v>
@@ -28283,7 +28283,7 @@
         <v>6</v>
       </c>
       <c r="X309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y309">
         <v>3</v>
@@ -28292,10 +28292,10 @@
         <v>2</v>
       </c>
       <c r="AA309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB309">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310" spans="1:28">
@@ -28321,7 +28321,7 @@
         <v>5</v>
       </c>
       <c r="H310">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I310">
         <v>3</v>
@@ -28336,7 +28336,7 @@
         <v>5</v>
       </c>
       <c r="M310">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N310">
         <v>4</v>
@@ -28351,13 +28351,13 @@
         <v>6</v>
       </c>
       <c r="R310">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S310">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T310">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U310">
         <v>7</v>
@@ -28369,7 +28369,7 @@
         <v>6</v>
       </c>
       <c r="X310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y310">
         <v>2</v>
@@ -28526,7 +28526,7 @@
         <v>5</v>
       </c>
       <c r="S312">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T312">
         <v>6</v>
@@ -28585,10 +28585,10 @@
         <v>3</v>
       </c>
       <c r="J313">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K313">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L313">
         <v>4</v>
@@ -28615,7 +28615,7 @@
         <v>6</v>
       </c>
       <c r="T313">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U313">
         <v>7</v>
@@ -28630,7 +28630,7 @@
         <v>1</v>
       </c>
       <c r="Y313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z313">
         <v>3</v>
@@ -28656,7 +28656,7 @@
         <v>422</v>
       </c>
       <c r="E314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F314">
         <v>5</v>
@@ -28677,7 +28677,7 @@
         <v>4</v>
       </c>
       <c r="L314">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M314">
         <v>3</v>
@@ -28843,7 +28843,7 @@
         <v>4</v>
       </c>
       <c r="J316">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K316">
         <v>4</v>
@@ -28888,7 +28888,7 @@
         <v>3</v>
       </c>
       <c r="Y316">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z316">
         <v>1</v>
@@ -28897,7 +28897,7 @@
         <v>2</v>
       </c>
       <c r="AB316">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317" spans="1:28">
@@ -28920,10 +28920,10 @@
         <v>3</v>
       </c>
       <c r="G317">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H317">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I317">
         <v>3</v>
@@ -28965,7 +28965,7 @@
         <v>5</v>
       </c>
       <c r="V317">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W317">
         <v>6</v>
@@ -29009,7 +29009,7 @@
         <v>3</v>
       </c>
       <c r="H318">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I318">
         <v>4</v>
@@ -29060,7 +29060,7 @@
         <v>3</v>
       </c>
       <c r="Y318">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z318">
         <v>2</v>
@@ -29089,7 +29089,7 @@
         <v>4</v>
       </c>
       <c r="F319">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G319">
         <v>4</v>
@@ -29101,7 +29101,7 @@
         <v>5</v>
       </c>
       <c r="J319">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K319">
         <v>4</v>
@@ -29110,7 +29110,7 @@
         <v>3</v>
       </c>
       <c r="M319">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N319">
         <v>4</v>
@@ -29122,7 +29122,7 @@
         <v>4</v>
       </c>
       <c r="Q319">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R319">
         <v>6</v>
@@ -29149,13 +29149,13 @@
         <v>4</v>
       </c>
       <c r="Z319">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA319">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB319">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:28">
@@ -29187,7 +29187,7 @@
         <v>3</v>
       </c>
       <c r="J320">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K320">
         <v>6</v>
@@ -29315,7 +29315,7 @@
         <v>6</v>
       </c>
       <c r="X321">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y321">
         <v>4</v>
@@ -29386,13 +29386,13 @@
         <v>5</v>
       </c>
       <c r="S322">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T322">
         <v>6</v>
       </c>
       <c r="U322">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V322">
         <v>6</v>
@@ -29404,16 +29404,16 @@
         <v>2</v>
       </c>
       <c r="Y322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z322">
         <v>3</v>
       </c>
       <c r="AA322">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB322">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="323" spans="1:28">
@@ -29478,7 +29478,7 @@
         <v>5</v>
       </c>
       <c r="U323">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V323">
         <v>6</v>
@@ -29516,16 +29516,16 @@
         <v>432</v>
       </c>
       <c r="E324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F324">
         <v>5</v>
       </c>
       <c r="G324">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H324">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I324">
         <v>2</v>
@@ -29534,22 +29534,22 @@
         <v>5</v>
       </c>
       <c r="K324">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L324">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M324">
         <v>5</v>
       </c>
       <c r="N324">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O324">
         <v>6</v>
       </c>
       <c r="P324">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q324">
         <v>6</v>
@@ -29641,19 +29641,19 @@
         <v>5</v>
       </c>
       <c r="R325">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S325">
         <v>6</v>
       </c>
       <c r="T325">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U325">
         <v>6</v>
       </c>
       <c r="V325">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W325">
         <v>6</v>
@@ -29691,7 +29691,7 @@
         <v>6</v>
       </c>
       <c r="F326">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G326">
         <v>6</v>
@@ -29712,7 +29712,7 @@
         <v>7</v>
       </c>
       <c r="M326">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N326">
         <v>2</v>
@@ -29748,13 +29748,13 @@
         <v>2</v>
       </c>
       <c r="Y326">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z326">
         <v>3</v>
       </c>
       <c r="AA326">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB326">
         <v>2</v>
@@ -29789,7 +29789,7 @@
         <v>2</v>
       </c>
       <c r="J327">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K327">
         <v>6</v>
@@ -29819,7 +29819,7 @@
         <v>5</v>
       </c>
       <c r="T327">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U327">
         <v>5</v>
@@ -29834,7 +29834,7 @@
         <v>2</v>
       </c>
       <c r="Y327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z327">
         <v>2</v>
@@ -29843,7 +29843,7 @@
         <v>2</v>
       </c>
       <c r="AB327">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="328" spans="1:28">
@@ -29878,10 +29878,10 @@
         <v>6</v>
       </c>
       <c r="K328">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L328">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M328">
         <v>6</v>
@@ -29896,7 +29896,7 @@
         <v>6</v>
       </c>
       <c r="Q328">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R328">
         <v>5</v>
@@ -29911,13 +29911,13 @@
         <v>5</v>
       </c>
       <c r="V328">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W328">
         <v>6</v>
       </c>
       <c r="X328">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y328">
         <v>2</v>
@@ -30006,7 +30006,7 @@
         <v>2</v>
       </c>
       <c r="Y329">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z329">
         <v>2</v>
@@ -30056,16 +30056,16 @@
         <v>5</v>
       </c>
       <c r="M330">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N330">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O330">
         <v>5</v>
       </c>
       <c r="P330">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q330">
         <v>4</v>
@@ -30074,10 +30074,10 @@
         <v>4</v>
       </c>
       <c r="S330">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T330">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U330">
         <v>4</v>
@@ -30204,7 +30204,7 @@
         <v>440</v>
       </c>
       <c r="E332">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F332">
         <v>6</v>
@@ -30222,13 +30222,13 @@
         <v>5</v>
       </c>
       <c r="K332">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L332">
         <v>5</v>
       </c>
       <c r="M332">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N332">
         <v>3</v>
@@ -30249,10 +30249,10 @@
         <v>6</v>
       </c>
       <c r="T332">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U332">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V332">
         <v>4</v>
@@ -30261,16 +30261,16 @@
         <v>6</v>
       </c>
       <c r="X332">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y332">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z332">
         <v>5</v>
       </c>
       <c r="AA332">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB332">
         <v>3</v>
@@ -30308,7 +30308,7 @@
         <v>5</v>
       </c>
       <c r="K333">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L333">
         <v>6</v>
@@ -30332,7 +30332,7 @@
         <v>6</v>
       </c>
       <c r="S333">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T333">
         <v>5</v>
@@ -30341,7 +30341,7 @@
         <v>6</v>
       </c>
       <c r="V333">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W333">
         <v>6</v>
@@ -30418,16 +30418,16 @@
         <v>5</v>
       </c>
       <c r="S334">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T334">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U334">
         <v>5</v>
       </c>
       <c r="V334">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W334">
         <v>6</v>
@@ -30439,7 +30439,7 @@
         <v>3</v>
       </c>
       <c r="Z334">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA334">
         <v>3</v>
@@ -30462,7 +30462,7 @@
         <v>443</v>
       </c>
       <c r="E335">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F335">
         <v>4</v>
@@ -30498,13 +30498,13 @@
         <v>5</v>
       </c>
       <c r="Q335">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R335">
         <v>7</v>
       </c>
       <c r="S335">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T335">
         <v>7</v>
@@ -30513,7 +30513,7 @@
         <v>5</v>
       </c>
       <c r="V335">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W335">
         <v>6</v>
@@ -30584,7 +30584,7 @@
         <v>5</v>
       </c>
       <c r="Q336">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R336">
         <v>3</v>
@@ -30611,7 +30611,7 @@
         <v>4</v>
       </c>
       <c r="Z336">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA336">
         <v>4</v>
@@ -30670,7 +30670,7 @@
         <v>5</v>
       </c>
       <c r="Q337">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R337">
         <v>7</v>
@@ -30682,7 +30682,7 @@
         <v>7</v>
       </c>
       <c r="U337">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V337">
         <v>7</v>
@@ -30691,7 +30691,7 @@
         <v>6</v>
       </c>
       <c r="X337">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y337">
         <v>3</v>
@@ -30700,10 +30700,10 @@
         <v>1</v>
       </c>
       <c r="AA337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB337">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="338" spans="1:28">
@@ -30726,7 +30726,7 @@
         <v>6</v>
       </c>
       <c r="G338">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H338">
         <v>6</v>
@@ -30756,7 +30756,7 @@
         <v>6</v>
       </c>
       <c r="Q338">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R338">
         <v>3</v>
@@ -30765,7 +30765,7 @@
         <v>5</v>
       </c>
       <c r="T338">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U338">
         <v>3</v>
@@ -30812,7 +30812,7 @@
         <v>5</v>
       </c>
       <c r="G339">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H339">
         <v>5</v>
@@ -30848,34 +30848,34 @@
         <v>5</v>
       </c>
       <c r="S339">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T339">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U339">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V339">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W339">
         <v>6</v>
       </c>
       <c r="X339">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y339">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z339">
         <v>2</v>
       </c>
       <c r="AA339">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB339">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="340" spans="1:28">
@@ -30901,13 +30901,13 @@
         <v>6</v>
       </c>
       <c r="H340">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I340">
         <v>2</v>
       </c>
       <c r="J340">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K340">
         <v>6</v>
@@ -30996,7 +30996,7 @@
         <v>4</v>
       </c>
       <c r="K341">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L341">
         <v>4</v>
@@ -31041,7 +31041,7 @@
         <v>2</v>
       </c>
       <c r="Z341">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA341">
         <v>3</v>
